--- a/compare/output/dscale_CO2_downscaled_SSP126.xlsx
+++ b/compare/output/dscale_CO2_downscaled_SSP126.xlsx
@@ -529,55 +529,55 @@
         <v>0.140198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.210694</v>
+        <v>0.210692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.232498</v>
+        <v>0.232496</v>
       </c>
       <c r="H2" t="n">
-        <v>0.254458</v>
+        <v>0.254455</v>
       </c>
       <c r="I2" t="n">
-        <v>0.266553</v>
+        <v>0.26655</v>
       </c>
       <c r="J2" t="n">
-        <v>0.263121</v>
+        <v>0.263118</v>
       </c>
       <c r="K2" t="n">
-        <v>0.262752</v>
+        <v>0.262749</v>
       </c>
       <c r="L2" t="n">
-        <v>0.269996</v>
+        <v>0.269993</v>
       </c>
       <c r="M2" t="n">
-        <v>0.29508</v>
+        <v>0.295077</v>
       </c>
       <c r="N2" t="n">
-        <v>0.330754</v>
+        <v>0.330751</v>
       </c>
       <c r="O2" t="n">
-        <v>0.38318</v>
+        <v>0.383177</v>
       </c>
       <c r="P2" t="n">
-        <v>0.441092</v>
+        <v>0.44109</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5060170000000001</v>
+        <v>0.506014</v>
       </c>
       <c r="R2" t="n">
-        <v>0.563061</v>
+        <v>0.5630579999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6012459999999999</v>
+        <v>0.601244</v>
       </c>
       <c r="T2" t="n">
-        <v>0.620631</v>
+        <v>0.620629</v>
       </c>
       <c r="U2" t="n">
-        <v>0.641236</v>
+        <v>0.6412330000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.662722</v>
+        <v>0.6627189999999999</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         <v>0.125289</v>
       </c>
       <c r="S3" t="n">
-        <v>0.125271</v>
+        <v>0.125272</v>
       </c>
       <c r="T3" t="n">
         <v>0.121928</v>
@@ -681,7 +681,7 @@
         <v>0.262894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.30175</v>
+        <v>0.301751</v>
       </c>
       <c r="G4" t="n">
         <v>0.264694</v>
@@ -702,13 +702,13 @@
         <v>0.218489</v>
       </c>
       <c r="M4" t="n">
-        <v>0.224426</v>
+        <v>0.224427</v>
       </c>
       <c r="N4" t="n">
-        <v>0.232782</v>
+        <v>0.232783</v>
       </c>
       <c r="O4" t="n">
-        <v>0.248091</v>
+        <v>0.248092</v>
       </c>
       <c r="P4" t="n">
         <v>0.263491</v>
@@ -729,7 +729,7 @@
         <v>0.310464</v>
       </c>
       <c r="V4" t="n">
-        <v>0.303334</v>
+        <v>0.303335</v>
       </c>
     </row>
     <row r="5">
@@ -766,7 +766,7 @@
         <v>0.561788</v>
       </c>
       <c r="I5" t="n">
-        <v>0.663562</v>
+        <v>0.663561</v>
       </c>
       <c r="J5" t="n">
         <v>0.6963859999999999</v>
@@ -778,7 +778,7 @@
         <v>0.721749</v>
       </c>
       <c r="M5" t="n">
-        <v>0.761772</v>
+        <v>0.761771</v>
       </c>
       <c r="N5" t="n">
         <v>0.8075870000000001</v>
@@ -805,7 +805,7 @@
         <v>1.134005</v>
       </c>
       <c r="V5" t="n">
-        <v>1.120984</v>
+        <v>1.120985</v>
       </c>
     </row>
     <row r="6">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.386256</v>
+        <v>4.386253</v>
       </c>
       <c r="F6" t="n">
-        <v>6.415477</v>
+        <v>6.41547</v>
       </c>
       <c r="G6" t="n">
-        <v>6.307835</v>
+        <v>6.307824</v>
       </c>
       <c r="H6" t="n">
-        <v>6.283219</v>
+        <v>6.283205</v>
       </c>
       <c r="I6" t="n">
-        <v>6.248941</v>
+        <v>6.248924</v>
       </c>
       <c r="J6" t="n">
-        <v>6.022163</v>
+        <v>6.022146</v>
       </c>
       <c r="K6" t="n">
-        <v>5.969065</v>
+        <v>5.969049</v>
       </c>
       <c r="L6" t="n">
-        <v>6.042996</v>
+        <v>6.04298</v>
       </c>
       <c r="M6" t="n">
-        <v>6.421665</v>
+        <v>6.421649</v>
       </c>
       <c r="N6" t="n">
-        <v>6.898094</v>
+        <v>6.898078</v>
       </c>
       <c r="O6" t="n">
-        <v>7.609853</v>
+        <v>7.609838</v>
       </c>
       <c r="P6" t="n">
-        <v>8.360969000000001</v>
+        <v>8.360954</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.407394999999999</v>
+        <v>9.407381000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>10.462032</v>
+        <v>10.46202</v>
       </c>
       <c r="S6" t="n">
-        <v>11.220315</v>
+        <v>11.220304</v>
       </c>
       <c r="T6" t="n">
-        <v>11.531715</v>
+        <v>11.531706</v>
       </c>
       <c r="U6" t="n">
-        <v>11.486337</v>
+        <v>11.486328</v>
       </c>
       <c r="V6" t="n">
-        <v>11.249477</v>
+        <v>11.249469</v>
       </c>
     </row>
     <row r="7">
@@ -906,58 +906,58 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.759589</v>
+        <v>5.759591</v>
       </c>
       <c r="F7" t="n">
-        <v>8.752413000000001</v>
+        <v>8.752420000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>10.296766</v>
+        <v>10.296777</v>
       </c>
       <c r="H7" t="n">
-        <v>12.38522</v>
+        <v>12.385236</v>
       </c>
       <c r="I7" t="n">
-        <v>14.160296</v>
+        <v>14.160317</v>
       </c>
       <c r="J7" t="n">
-        <v>14.9236</v>
+        <v>14.923623</v>
       </c>
       <c r="K7" t="n">
-        <v>15.388893</v>
+        <v>15.388918</v>
       </c>
       <c r="L7" t="n">
-        <v>15.597601</v>
+        <v>15.597627</v>
       </c>
       <c r="M7" t="n">
-        <v>16.086786</v>
+        <v>16.086812</v>
       </c>
       <c r="N7" t="n">
-        <v>16.397288</v>
+        <v>16.397314</v>
       </c>
       <c r="O7" t="n">
-        <v>16.897051</v>
+        <v>16.897076</v>
       </c>
       <c r="P7" t="n">
-        <v>17.203017</v>
+        <v>17.203042</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.600242</v>
+        <v>17.600266</v>
       </c>
       <c r="R7" t="n">
-        <v>17.719488</v>
+        <v>17.719511</v>
       </c>
       <c r="S7" t="n">
-        <v>17.379712</v>
+        <v>17.379735</v>
       </c>
       <c r="T7" t="n">
-        <v>16.683243</v>
+        <v>16.683264</v>
       </c>
       <c r="U7" t="n">
-        <v>15.832664</v>
+        <v>15.832684</v>
       </c>
       <c r="V7" t="n">
-        <v>15.000959</v>
+        <v>15.000978</v>
       </c>
     </row>
     <row r="8">
@@ -982,58 +982,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.109707</v>
+        <v>1.109706</v>
       </c>
       <c r="F8" t="n">
-        <v>1.617299</v>
+        <v>1.617298</v>
       </c>
       <c r="G8" t="n">
-        <v>1.747773</v>
+        <v>1.747771</v>
       </c>
       <c r="H8" t="n">
-        <v>1.896236</v>
+        <v>1.896233</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9876</v>
+        <v>1.987596</v>
       </c>
       <c r="J8" t="n">
-        <v>1.964458</v>
+        <v>1.964454</v>
       </c>
       <c r="K8" t="n">
-        <v>1.953574</v>
+        <v>1.953571</v>
       </c>
       <c r="L8" t="n">
-        <v>1.970948</v>
+        <v>1.970945</v>
       </c>
       <c r="M8" t="n">
-        <v>2.07332</v>
+        <v>2.073316</v>
       </c>
       <c r="N8" t="n">
-        <v>2.194906</v>
+        <v>2.194903</v>
       </c>
       <c r="O8" t="n">
-        <v>2.378756</v>
+        <v>2.378752</v>
       </c>
       <c r="P8" t="n">
-        <v>2.570657</v>
+        <v>2.570654</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.803597</v>
+        <v>2.803593</v>
       </c>
       <c r="R8" t="n">
-        <v>3.016745</v>
+        <v>3.016742</v>
       </c>
       <c r="S8" t="n">
-        <v>3.153358</v>
+        <v>3.153355</v>
       </c>
       <c r="T8" t="n">
-        <v>3.199529</v>
+        <v>3.199527</v>
       </c>
       <c r="U8" t="n">
-        <v>3.174321</v>
+        <v>3.174319</v>
       </c>
       <c r="V8" t="n">
-        <v>3.107409</v>
+        <v>3.107408</v>
       </c>
     </row>
     <row r="9">
@@ -1058,58 +1058,58 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.299168</v>
+        <v>1.299169</v>
       </c>
       <c r="F9" t="n">
-        <v>1.457957</v>
+        <v>1.457959</v>
       </c>
       <c r="G9" t="n">
-        <v>1.194722</v>
+        <v>1.194724</v>
       </c>
       <c r="H9" t="n">
-        <v>1.037346</v>
+        <v>1.037348</v>
       </c>
       <c r="I9" t="n">
-        <v>0.910409</v>
+        <v>0.910411</v>
       </c>
       <c r="J9" t="n">
-        <v>0.78588</v>
+        <v>0.7858810000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.697472</v>
+        <v>0.697474</v>
       </c>
       <c r="L9" t="n">
-        <v>0.638281</v>
+        <v>0.638282</v>
       </c>
       <c r="M9" t="n">
-        <v>0.612007</v>
+        <v>0.612009</v>
       </c>
       <c r="N9" t="n">
-        <v>0.588741</v>
+        <v>0.588742</v>
       </c>
       <c r="O9" t="n">
-        <v>0.575512</v>
+        <v>0.575514</v>
       </c>
       <c r="P9" t="n">
-        <v>0.571534</v>
+        <v>0.571535</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.578731</v>
+        <v>0.578732</v>
       </c>
       <c r="R9" t="n">
-        <v>0.580952</v>
+        <v>0.5809530000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.566891</v>
+        <v>0.566892</v>
       </c>
       <c r="T9" t="n">
-        <v>0.540276</v>
+        <v>0.540277</v>
       </c>
       <c r="U9" t="n">
-        <v>0.506896</v>
+        <v>0.506897</v>
       </c>
       <c r="V9" t="n">
-        <v>0.47289</v>
+        <v>0.472891</v>
       </c>
     </row>
     <row r="10">
@@ -1137,55 +1137,55 @@
         <v>0.358596</v>
       </c>
       <c r="F10" t="n">
-        <v>0.488814</v>
+        <v>0.488813</v>
       </c>
       <c r="G10" t="n">
-        <v>0.471769</v>
+        <v>0.471767</v>
       </c>
       <c r="H10" t="n">
-        <v>0.47353</v>
+        <v>0.473528</v>
       </c>
       <c r="I10" t="n">
-        <v>0.472613</v>
+        <v>0.47261</v>
       </c>
       <c r="J10" t="n">
-        <v>0.458063</v>
+        <v>0.45806</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457388</v>
+        <v>0.457384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.470943</v>
+        <v>0.47094</v>
       </c>
       <c r="M10" t="n">
-        <v>0.510087</v>
+        <v>0.510084</v>
       </c>
       <c r="N10" t="n">
-        <v>0.559962</v>
+        <v>0.559959</v>
       </c>
       <c r="O10" t="n">
-        <v>0.628443</v>
+        <v>0.628439</v>
       </c>
       <c r="P10" t="n">
-        <v>0.697615</v>
+        <v>0.697612</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7721749999999999</v>
+        <v>0.7721710000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>0.835696</v>
+        <v>0.835692</v>
       </c>
       <c r="S10" t="n">
-        <v>0.891621</v>
+        <v>0.891618</v>
       </c>
       <c r="T10" t="n">
-        <v>0.935211</v>
+        <v>0.935207</v>
       </c>
       <c r="U10" t="n">
-        <v>0.96413</v>
+        <v>0.964126</v>
       </c>
       <c r="V10" t="n">
-        <v>0.978063</v>
+        <v>0.978059</v>
       </c>
     </row>
     <row r="11">
@@ -1210,58 +1210,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.000406</v>
+        <v>7.00041</v>
       </c>
       <c r="F11" t="n">
-        <v>9.880585999999999</v>
+        <v>9.880594</v>
       </c>
       <c r="G11" t="n">
-        <v>10.397636</v>
+        <v>10.397646</v>
       </c>
       <c r="H11" t="n">
-        <v>11.201711</v>
+        <v>11.201724</v>
       </c>
       <c r="I11" t="n">
-        <v>11.621976</v>
+        <v>11.621989</v>
       </c>
       <c r="J11" t="n">
-        <v>10.890549</v>
+        <v>10.890561</v>
       </c>
       <c r="K11" t="n">
-        <v>10.113102</v>
+        <v>10.113112</v>
       </c>
       <c r="L11" t="n">
-        <v>9.559538999999999</v>
+        <v>9.559547</v>
       </c>
       <c r="M11" t="n">
-        <v>9.614265</v>
+        <v>9.614273000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>9.86199</v>
+        <v>9.861998</v>
       </c>
       <c r="O11" t="n">
-        <v>10.384897</v>
+        <v>10.384905</v>
       </c>
       <c r="P11" t="n">
-        <v>10.82519</v>
+        <v>10.825199</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.272352</v>
+        <v>11.272361</v>
       </c>
       <c r="R11" t="n">
-        <v>11.447133</v>
+        <v>11.447143</v>
       </c>
       <c r="S11" t="n">
-        <v>11.22028</v>
+        <v>11.220289</v>
       </c>
       <c r="T11" t="n">
-        <v>10.679792</v>
+        <v>10.6798</v>
       </c>
       <c r="U11" t="n">
-        <v>9.995839</v>
+        <v>9.995846</v>
       </c>
       <c r="V11" t="n">
-        <v>9.337393</v>
+        <v>9.337400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1289,52 +1289,52 @@
         <v>0.264835</v>
       </c>
       <c r="F12" t="n">
-        <v>0.390747</v>
+        <v>0.390746</v>
       </c>
       <c r="G12" t="n">
-        <v>0.439635</v>
+        <v>0.439633</v>
       </c>
       <c r="H12" t="n">
-        <v>0.50099</v>
+        <v>0.500988</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5428770000000001</v>
+        <v>0.542875</v>
       </c>
       <c r="J12" t="n">
-        <v>0.553214</v>
+        <v>0.553212</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5616950000000001</v>
+        <v>0.561693</v>
       </c>
       <c r="L12" t="n">
-        <v>0.575686</v>
+        <v>0.575685</v>
       </c>
       <c r="M12" t="n">
-        <v>0.611415</v>
+        <v>0.611414</v>
       </c>
       <c r="N12" t="n">
-        <v>0.649304</v>
+        <v>0.649303</v>
       </c>
       <c r="O12" t="n">
-        <v>0.705558</v>
+        <v>0.705557</v>
       </c>
       <c r="P12" t="n">
-        <v>0.766871</v>
+        <v>0.7668700000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8444390000000001</v>
+        <v>0.844438</v>
       </c>
       <c r="R12" t="n">
-        <v>0.916624</v>
+        <v>0.916623</v>
       </c>
       <c r="S12" t="n">
         <v>0.96635</v>
       </c>
       <c r="T12" t="n">
-        <v>0.991286</v>
+        <v>0.991285</v>
       </c>
       <c r="U12" t="n">
-        <v>0.999143</v>
+        <v>0.999142</v>
       </c>
       <c r="V12" t="n">
         <v>1.000532</v>
@@ -1362,58 +1362,58 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.745046</v>
+        <v>1.745045</v>
       </c>
       <c r="F13" t="n">
-        <v>2.54925</v>
+        <v>2.549247</v>
       </c>
       <c r="G13" t="n">
-        <v>2.70716</v>
+        <v>2.707155</v>
       </c>
       <c r="H13" t="n">
-        <v>2.968338</v>
+        <v>2.968331</v>
       </c>
       <c r="I13" t="n">
-        <v>3.208851</v>
+        <v>3.208843</v>
       </c>
       <c r="J13" t="n">
-        <v>3.31389</v>
+        <v>3.313881</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45871</v>
+        <v>3.458702</v>
       </c>
       <c r="L13" t="n">
-        <v>3.644851</v>
+        <v>3.644842</v>
       </c>
       <c r="M13" t="n">
-        <v>3.965212</v>
+        <v>3.965204</v>
       </c>
       <c r="N13" t="n">
-        <v>4.282303</v>
+        <v>4.282294</v>
       </c>
       <c r="O13" t="n">
-        <v>4.670613</v>
+        <v>4.670604</v>
       </c>
       <c r="P13" t="n">
-        <v>5.013701</v>
+        <v>5.013692</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.38369</v>
+        <v>5.383679</v>
       </c>
       <c r="R13" t="n">
-        <v>5.672685</v>
+        <v>5.672674</v>
       </c>
       <c r="S13" t="n">
-        <v>5.865971</v>
+        <v>5.865959</v>
       </c>
       <c r="T13" t="n">
-        <v>5.956811</v>
+        <v>5.9568</v>
       </c>
       <c r="U13" t="n">
-        <v>5.967732</v>
+        <v>5.967721</v>
       </c>
       <c r="V13" t="n">
-        <v>5.928394</v>
+        <v>5.928383</v>
       </c>
     </row>
     <row r="14">
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44.333037</v>
+        <v>44.333562</v>
       </c>
       <c r="F14" t="n">
-        <v>51.070694</v>
+        <v>51.071656</v>
       </c>
       <c r="G14" t="n">
-        <v>53.08044</v>
+        <v>53.081746</v>
       </c>
       <c r="H14" t="n">
-        <v>55.682583</v>
+        <v>55.68419</v>
       </c>
       <c r="I14" t="n">
-        <v>56.600327</v>
+        <v>56.602115</v>
       </c>
       <c r="J14" t="n">
-        <v>56.64555</v>
+        <v>56.647427</v>
       </c>
       <c r="K14" t="n">
-        <v>55.900004</v>
+        <v>55.901885</v>
       </c>
       <c r="L14" t="n">
-        <v>54.341633</v>
+        <v>54.343457</v>
       </c>
       <c r="M14" t="n">
-        <v>52.0664</v>
+        <v>52.068143</v>
       </c>
       <c r="N14" t="n">
-        <v>48.674016</v>
+        <v>48.675663</v>
       </c>
       <c r="O14" t="n">
-        <v>44.220211</v>
+        <v>44.221758</v>
       </c>
       <c r="P14" t="n">
-        <v>40.313245</v>
+        <v>40.314731</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.596248</v>
+        <v>35.597656</v>
       </c>
       <c r="R14" t="n">
-        <v>30.988676</v>
+        <v>30.990013</v>
       </c>
       <c r="S14" t="n">
-        <v>26.641992</v>
+        <v>26.643275</v>
       </c>
       <c r="T14" t="n">
-        <v>22.747241</v>
+        <v>22.7485</v>
       </c>
       <c r="U14" t="n">
-        <v>19.34142</v>
+        <v>19.34269</v>
       </c>
       <c r="V14" t="n">
-        <v>16.224176</v>
+        <v>16.225485</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64.378883</v>
+        <v>64.378552</v>
       </c>
       <c r="F15" t="n">
-        <v>81.424397</v>
+        <v>81.42400600000001</v>
       </c>
       <c r="G15" t="n">
-        <v>88.392596</v>
+        <v>88.392346</v>
       </c>
       <c r="H15" t="n">
-        <v>94.580061</v>
+        <v>94.579956</v>
       </c>
       <c r="I15" t="n">
-        <v>96.795106</v>
+        <v>96.795062</v>
       </c>
       <c r="J15" t="n">
-        <v>96.80901799999999</v>
+        <v>96.808949</v>
       </c>
       <c r="K15" t="n">
-        <v>95.267228</v>
+        <v>95.26705800000001</v>
       </c>
       <c r="L15" t="n">
-        <v>92.559382</v>
+        <v>92.559067</v>
       </c>
       <c r="M15" t="n">
-        <v>89.000429</v>
+        <v>88.99995199999999</v>
       </c>
       <c r="N15" t="n">
-        <v>83.82951799999999</v>
+        <v>83.828895</v>
       </c>
       <c r="O15" t="n">
-        <v>76.96652</v>
+        <v>76.965789</v>
       </c>
       <c r="P15" t="n">
-        <v>71.055644</v>
+        <v>71.05482000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.595132</v>
+        <v>63.594252</v>
       </c>
       <c r="R15" t="n">
-        <v>56.110058</v>
+        <v>56.109134</v>
       </c>
       <c r="S15" t="n">
-        <v>48.723811</v>
+        <v>48.722835</v>
       </c>
       <c r="T15" t="n">
-        <v>41.821032</v>
+        <v>41.820002</v>
       </c>
       <c r="U15" t="n">
-        <v>35.635674</v>
+        <v>35.634594</v>
       </c>
       <c r="V15" t="n">
-        <v>29.931747</v>
+        <v>29.930617</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14.706019</v>
+        <v>14.70643</v>
       </c>
       <c r="F16" t="n">
-        <v>14.556907</v>
+        <v>14.557562</v>
       </c>
       <c r="G16" t="n">
-        <v>12.546043</v>
+        <v>12.546675</v>
       </c>
       <c r="H16" t="n">
-        <v>11.337788</v>
+        <v>11.338325</v>
       </c>
       <c r="I16" t="n">
-        <v>10.405859</v>
+        <v>10.40629</v>
       </c>
       <c r="J16" t="n">
-        <v>9.776975999999999</v>
+        <v>9.777324999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>9.333207</v>
+        <v>9.333500000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>8.969671</v>
+        <v>8.969929</v>
       </c>
       <c r="M16" t="n">
-        <v>8.645397000000001</v>
+        <v>8.645640999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>8.203061999999999</v>
+        <v>8.203301</v>
       </c>
       <c r="O16" t="n">
-        <v>7.588923</v>
+        <v>7.589159</v>
       </c>
       <c r="P16" t="n">
-        <v>7.089105</v>
+        <v>7.089351</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.468091</v>
+        <v>6.468352</v>
       </c>
       <c r="R16" t="n">
-        <v>5.864077</v>
+        <v>5.864363</v>
       </c>
       <c r="S16" t="n">
-        <v>5.260508</v>
+        <v>5.260826</v>
       </c>
       <c r="T16" t="n">
-        <v>4.652515</v>
+        <v>4.652864</v>
       </c>
       <c r="U16" t="n">
-        <v>4.054547</v>
+        <v>4.054924</v>
       </c>
       <c r="V16" t="n">
-        <v>3.446768</v>
+        <v>3.447167</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16.441512</v>
+        <v>16.440912</v>
       </c>
       <c r="F17" t="n">
-        <v>19.404265</v>
+        <v>19.403028</v>
       </c>
       <c r="G17" t="n">
-        <v>19.936652</v>
+        <v>19.934992</v>
       </c>
       <c r="H17" t="n">
-        <v>20.308725</v>
+        <v>20.30678</v>
       </c>
       <c r="I17" t="n">
-        <v>19.971455</v>
+        <v>19.969416</v>
       </c>
       <c r="J17" t="n">
-        <v>19.297623</v>
+        <v>19.295596</v>
       </c>
       <c r="K17" t="n">
-        <v>18.789193</v>
+        <v>18.787292</v>
       </c>
       <c r="L17" t="n">
-        <v>18.509783</v>
+        <v>18.508085</v>
       </c>
       <c r="M17" t="n">
-        <v>18.371344</v>
+        <v>18.369886</v>
       </c>
       <c r="N17" t="n">
-        <v>17.938031</v>
+        <v>17.93682</v>
       </c>
       <c r="O17" t="n">
-        <v>17.010306</v>
+        <v>17.009322</v>
       </c>
       <c r="P17" t="n">
-        <v>16.087122</v>
+        <v>16.086304</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.615277</v>
+        <v>14.614597</v>
       </c>
       <c r="R17" t="n">
-        <v>12.988842</v>
+        <v>12.988261</v>
       </c>
       <c r="S17" t="n">
-        <v>11.302743</v>
+        <v>11.302231</v>
       </c>
       <c r="T17" t="n">
-        <v>9.641899</v>
+        <v>9.641420999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>8.078604</v>
+        <v>8.078120999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>6.646195</v>
+        <v>6.64569</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.260731</v>
+        <v>8.260725000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>9.996779999999999</v>
+        <v>9.996791</v>
       </c>
       <c r="G18" t="n">
-        <v>9.944114000000001</v>
+        <v>9.944086</v>
       </c>
       <c r="H18" t="n">
-        <v>9.810689</v>
+        <v>9.810594999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>9.514749</v>
+        <v>9.514613000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>9.353528000000001</v>
+        <v>9.353398</v>
       </c>
       <c r="K18" t="n">
-        <v>9.23465</v>
+        <v>9.234548</v>
       </c>
       <c r="L18" t="n">
-        <v>9.08137</v>
+        <v>9.081300000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>8.770128</v>
+        <v>8.770076</v>
       </c>
       <c r="N18" t="n">
-        <v>8.168761999999999</v>
+        <v>8.168711</v>
       </c>
       <c r="O18" t="n">
-        <v>7.303452</v>
+        <v>7.303385</v>
       </c>
       <c r="P18" t="n">
-        <v>6.507484</v>
+        <v>6.507394</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.614711</v>
+        <v>5.6146</v>
       </c>
       <c r="R18" t="n">
-        <v>4.821849</v>
+        <v>4.82173</v>
       </c>
       <c r="S18" t="n">
-        <v>4.135968</v>
+        <v>4.135854</v>
       </c>
       <c r="T18" t="n">
-        <v>3.539627</v>
+        <v>3.539527</v>
       </c>
       <c r="U18" t="n">
-        <v>3.010091</v>
+        <v>3.010006</v>
       </c>
       <c r="V18" t="n">
-        <v>2.516167</v>
+        <v>2.516094</v>
       </c>
     </row>
     <row r="19">
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.890772</v>
+        <v>8.890841</v>
       </c>
       <c r="F19" t="n">
-        <v>12.580483</v>
+        <v>12.580646</v>
       </c>
       <c r="G19" t="n">
-        <v>13.30301</v>
+        <v>13.303222</v>
       </c>
       <c r="H19" t="n">
-        <v>13.839864</v>
+        <v>13.840102</v>
       </c>
       <c r="I19" t="n">
-        <v>14.200294</v>
+        <v>14.200539</v>
       </c>
       <c r="J19" t="n">
-        <v>14.413634</v>
+        <v>14.413875</v>
       </c>
       <c r="K19" t="n">
-        <v>15.198745</v>
+        <v>15.198989</v>
       </c>
       <c r="L19" t="n">
-        <v>16.761675</v>
+        <v>16.76193</v>
       </c>
       <c r="M19" t="n">
-        <v>18.547485</v>
+        <v>18.547754</v>
       </c>
       <c r="N19" t="n">
-        <v>20.030204</v>
+        <v>20.030483</v>
       </c>
       <c r="O19" t="n">
-        <v>20.003131</v>
+        <v>20.003401</v>
       </c>
       <c r="P19" t="n">
-        <v>19.249775</v>
+        <v>19.25003</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.406655</v>
+        <v>17.406886</v>
       </c>
       <c r="R19" t="n">
-        <v>14.990744</v>
+        <v>14.990947</v>
       </c>
       <c r="S19" t="n">
-        <v>12.320431</v>
+        <v>12.320606</v>
       </c>
       <c r="T19" t="n">
-        <v>9.844753000000001</v>
+        <v>9.844905000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>7.793284</v>
+        <v>7.793419</v>
       </c>
       <c r="V19" t="n">
-        <v>6.301185</v>
+        <v>6.301313</v>
       </c>
     </row>
     <row r="20">
@@ -1894,58 +1894,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.903904</v>
+        <v>1.903923</v>
       </c>
       <c r="F20" t="n">
-        <v>2.461017</v>
+        <v>2.461058</v>
       </c>
       <c r="G20" t="n">
-        <v>2.579905</v>
+        <v>2.579959</v>
       </c>
       <c r="H20" t="n">
-        <v>2.653787</v>
+        <v>2.653848</v>
       </c>
       <c r="I20" t="n">
-        <v>2.620772</v>
+        <v>2.620834</v>
       </c>
       <c r="J20" t="n">
-        <v>2.477889</v>
+        <v>2.477946</v>
       </c>
       <c r="K20" t="n">
-        <v>2.371305</v>
+        <v>2.371357</v>
       </c>
       <c r="L20" t="n">
-        <v>2.328251</v>
+        <v>2.3283</v>
       </c>
       <c r="M20" t="n">
-        <v>2.279713</v>
+        <v>2.279758</v>
       </c>
       <c r="N20" t="n">
-        <v>2.183057</v>
+        <v>2.183097</v>
       </c>
       <c r="O20" t="n">
-        <v>1.944552</v>
+        <v>1.944585</v>
       </c>
       <c r="P20" t="n">
-        <v>1.680536</v>
+        <v>1.680564</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.375876</v>
+        <v>1.375898</v>
       </c>
       <c r="R20" t="n">
-        <v>1.081127</v>
+        <v>1.081144</v>
       </c>
       <c r="S20" t="n">
-        <v>0.817119</v>
+        <v>0.817132</v>
       </c>
       <c r="T20" t="n">
-        <v>0.605648</v>
+        <v>0.605658</v>
       </c>
       <c r="U20" t="n">
-        <v>0.448729</v>
+        <v>0.448737</v>
       </c>
       <c r="V20" t="n">
-        <v>0.342505</v>
+        <v>0.342512</v>
       </c>
     </row>
     <row r="21">
@@ -1970,58 +1970,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.158917</v>
+        <v>0.158915</v>
       </c>
       <c r="F21" t="n">
-        <v>0.181266</v>
+        <v>0.18126</v>
       </c>
       <c r="G21" t="n">
-        <v>0.168233</v>
+        <v>0.168225</v>
       </c>
       <c r="H21" t="n">
-        <v>0.165391</v>
+        <v>0.165383</v>
       </c>
       <c r="I21" t="n">
-        <v>0.166815</v>
+        <v>0.166806</v>
       </c>
       <c r="J21" t="n">
-        <v>0.168905</v>
+        <v>0.168896</v>
       </c>
       <c r="K21" t="n">
-        <v>0.177443</v>
+        <v>0.177434</v>
       </c>
       <c r="L21" t="n">
-        <v>0.193575</v>
+        <v>0.193566</v>
       </c>
       <c r="M21" t="n">
-        <v>0.210829</v>
+        <v>0.21082</v>
       </c>
       <c r="N21" t="n">
-        <v>0.223612</v>
+        <v>0.223602</v>
       </c>
       <c r="O21" t="n">
-        <v>0.223193</v>
+        <v>0.223185</v>
       </c>
       <c r="P21" t="n">
-        <v>0.216307</v>
+        <v>0.216299</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.19617</v>
+        <v>0.196163</v>
       </c>
       <c r="R21" t="n">
-        <v>0.166956</v>
+        <v>0.16695</v>
       </c>
       <c r="S21" t="n">
-        <v>0.133795</v>
+        <v>0.133791</v>
       </c>
       <c r="T21" t="n">
-        <v>0.103457</v>
+        <v>0.103453</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07913000000000001</v>
+        <v>0.079126</v>
       </c>
       <c r="V21" t="n">
-        <v>0.061972</v>
+        <v>0.061969</v>
       </c>
     </row>
     <row r="22">
@@ -2046,58 +2046,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.734825</v>
+        <v>1.734797</v>
       </c>
       <c r="F22" t="n">
-        <v>2.475236</v>
+        <v>2.475175</v>
       </c>
       <c r="G22" t="n">
-        <v>2.640631</v>
+        <v>2.640551</v>
       </c>
       <c r="H22" t="n">
-        <v>2.751688</v>
+        <v>2.751594</v>
       </c>
       <c r="I22" t="n">
-        <v>2.824136</v>
+        <v>2.824033</v>
       </c>
       <c r="J22" t="n">
-        <v>2.831331</v>
+        <v>2.831223</v>
       </c>
       <c r="K22" t="n">
-        <v>2.946029</v>
+        <v>2.945915</v>
       </c>
       <c r="L22" t="n">
-        <v>3.230629</v>
+        <v>3.230505</v>
       </c>
       <c r="M22" t="n">
-        <v>3.612515</v>
+        <v>3.612383</v>
       </c>
       <c r="N22" t="n">
-        <v>3.994002</v>
+        <v>3.993868</v>
       </c>
       <c r="O22" t="n">
-        <v>4.115729</v>
+        <v>4.115601</v>
       </c>
       <c r="P22" t="n">
-        <v>4.096355</v>
+        <v>4.096238</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.827409</v>
+        <v>3.827307</v>
       </c>
       <c r="R22" t="n">
-        <v>3.391224</v>
+        <v>3.391137</v>
       </c>
       <c r="S22" t="n">
-        <v>2.849242</v>
+        <v>2.84917</v>
       </c>
       <c r="T22" t="n">
-        <v>2.311944</v>
+        <v>2.311884</v>
       </c>
       <c r="U22" t="n">
-        <v>1.847141</v>
+        <v>1.847089</v>
       </c>
       <c r="V22" t="n">
-        <v>1.499932</v>
+        <v>1.499884</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.316269</v>
+        <v>1.316251</v>
       </c>
       <c r="F23" t="n">
-        <v>1.943079</v>
+        <v>1.943038</v>
       </c>
       <c r="G23" t="n">
-        <v>2.208105</v>
+        <v>2.208049</v>
       </c>
       <c r="H23" t="n">
-        <v>2.510499</v>
+        <v>2.510436</v>
       </c>
       <c r="I23" t="n">
-        <v>2.808249</v>
+        <v>2.80818</v>
       </c>
       <c r="J23" t="n">
-        <v>3.087131</v>
+        <v>3.08706</v>
       </c>
       <c r="K23" t="n">
-        <v>3.491126</v>
+        <v>3.491051</v>
       </c>
       <c r="L23" t="n">
-        <v>4.099669</v>
+        <v>4.099588</v>
       </c>
       <c r="M23" t="n">
-        <v>4.805348</v>
+        <v>4.805262</v>
       </c>
       <c r="N23" t="n">
-        <v>5.490084</v>
+        <v>5.489995</v>
       </c>
       <c r="O23" t="n">
-        <v>5.801092</v>
+        <v>5.801008</v>
       </c>
       <c r="P23" t="n">
-        <v>5.903119</v>
+        <v>5.903042</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.629157</v>
+        <v>5.62909</v>
       </c>
       <c r="R23" t="n">
-        <v>5.084514</v>
+        <v>5.084457</v>
       </c>
       <c r="S23" t="n">
-        <v>4.355246</v>
+        <v>4.355199</v>
       </c>
       <c r="T23" t="n">
-        <v>3.608474</v>
+        <v>3.608435</v>
       </c>
       <c r="U23" t="n">
-        <v>2.951336</v>
+        <v>2.951302</v>
       </c>
       <c r="V23" t="n">
-        <v>2.459974</v>
+        <v>2.459942</v>
       </c>
     </row>
     <row r="24">
@@ -2198,58 +2198,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.110612</v>
+        <v>1.110621</v>
       </c>
       <c r="F24" t="n">
-        <v>1.446148</v>
+        <v>1.446167</v>
       </c>
       <c r="G24" t="n">
-        <v>1.484173</v>
+        <v>1.484198</v>
       </c>
       <c r="H24" t="n">
-        <v>1.515846</v>
+        <v>1.515874</v>
       </c>
       <c r="I24" t="n">
-        <v>1.510421</v>
+        <v>1.510449</v>
       </c>
       <c r="J24" t="n">
-        <v>1.467743</v>
+        <v>1.46777</v>
       </c>
       <c r="K24" t="n">
-        <v>1.456937</v>
+        <v>1.456962</v>
       </c>
       <c r="L24" t="n">
-        <v>1.486871</v>
+        <v>1.486894</v>
       </c>
       <c r="M24" t="n">
-        <v>1.503369</v>
+        <v>1.503391</v>
       </c>
       <c r="N24" t="n">
-        <v>1.470594</v>
+        <v>1.470613</v>
       </c>
       <c r="O24" t="n">
-        <v>1.324689</v>
+        <v>1.324704</v>
       </c>
       <c r="P24" t="n">
-        <v>1.149005</v>
+        <v>1.149017</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.938862</v>
+        <v>0.938871</v>
       </c>
       <c r="R24" t="n">
-        <v>0.734242</v>
+        <v>0.734248</v>
       </c>
       <c r="S24" t="n">
-        <v>0.554546</v>
+        <v>0.55455</v>
       </c>
       <c r="T24" t="n">
-        <v>0.413687</v>
+        <v>0.41369</v>
       </c>
       <c r="U24" t="n">
-        <v>0.310606</v>
+        <v>0.310608</v>
       </c>
       <c r="V24" t="n">
-        <v>0.241352</v>
+        <v>0.241354</v>
       </c>
     </row>
     <row r="25">
@@ -2274,34 +2274,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.274167</v>
+        <v>0.274168</v>
       </c>
       <c r="F25" t="n">
-        <v>0.332034</v>
+        <v>0.332036</v>
       </c>
       <c r="G25" t="n">
-        <v>0.329994</v>
+        <v>0.329996</v>
       </c>
       <c r="H25" t="n">
-        <v>0.341268</v>
+        <v>0.341271</v>
       </c>
       <c r="I25" t="n">
-        <v>0.34778</v>
+        <v>0.347783</v>
       </c>
       <c r="J25" t="n">
-        <v>0.344875</v>
+        <v>0.344877</v>
       </c>
       <c r="K25" t="n">
-        <v>0.348385</v>
+        <v>0.348388</v>
       </c>
       <c r="L25" t="n">
-        <v>0.362186</v>
+        <v>0.362189</v>
       </c>
       <c r="M25" t="n">
-        <v>0.373447</v>
+        <v>0.373448</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372781</v>
+        <v>0.372782</v>
       </c>
       <c r="O25" t="n">
         <v>0.342485</v>
@@ -2310,22 +2310,22 @@
         <v>0.302461</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.251182</v>
+        <v>0.251181</v>
       </c>
       <c r="R25" t="n">
-        <v>0.199143</v>
+        <v>0.199142</v>
       </c>
       <c r="S25" t="n">
-        <v>0.151353</v>
+        <v>0.151352</v>
       </c>
       <c r="T25" t="n">
-        <v>0.112621</v>
+        <v>0.11262</v>
       </c>
       <c r="U25" t="n">
-        <v>0.08408400000000001</v>
+        <v>0.084083</v>
       </c>
       <c r="V25" t="n">
-        <v>0.06539499999999999</v>
+        <v>0.06539399999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.547005</v>
+        <v>3.546956</v>
       </c>
       <c r="F26" t="n">
-        <v>4.922068</v>
+        <v>4.921953</v>
       </c>
       <c r="G26" t="n">
-        <v>4.949345</v>
+        <v>4.94918</v>
       </c>
       <c r="H26" t="n">
-        <v>4.853106</v>
+        <v>4.852893</v>
       </c>
       <c r="I26" t="n">
-        <v>4.737492</v>
+        <v>4.737242</v>
       </c>
       <c r="J26" t="n">
-        <v>4.652893</v>
+        <v>4.65262</v>
       </c>
       <c r="K26" t="n">
-        <v>4.822964</v>
+        <v>4.822666</v>
       </c>
       <c r="L26" t="n">
-        <v>5.292798</v>
+        <v>5.29247</v>
       </c>
       <c r="M26" t="n">
-        <v>5.851911</v>
+        <v>5.851553</v>
       </c>
       <c r="N26" t="n">
-        <v>6.314057</v>
+        <v>6.313676</v>
       </c>
       <c r="O26" t="n">
-        <v>6.294371</v>
+        <v>6.293993</v>
       </c>
       <c r="P26" t="n">
-        <v>6.038952</v>
+        <v>6.038587</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.438791</v>
+        <v>5.438455</v>
       </c>
       <c r="R26" t="n">
-        <v>4.67706</v>
+        <v>4.67676</v>
       </c>
       <c r="S26" t="n">
-        <v>3.852426</v>
+        <v>3.852164</v>
       </c>
       <c r="T26" t="n">
-        <v>3.092906</v>
+        <v>3.092679</v>
       </c>
       <c r="U26" t="n">
-        <v>2.462072</v>
+        <v>2.461869</v>
       </c>
       <c r="V26" t="n">
-        <v>1.999614</v>
+        <v>1.999419</v>
       </c>
     </row>
     <row r="27">
@@ -2426,58 +2426,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.429142</v>
+        <v>1.429134</v>
       </c>
       <c r="F27" t="n">
-        <v>1.998707</v>
+        <v>1.998688</v>
       </c>
       <c r="G27" t="n">
-        <v>2.074293</v>
+        <v>2.074265</v>
       </c>
       <c r="H27" t="n">
-        <v>2.159785</v>
+        <v>2.15975</v>
       </c>
       <c r="I27" t="n">
-        <v>2.237838</v>
+        <v>2.237796</v>
       </c>
       <c r="J27" t="n">
-        <v>2.30548</v>
+        <v>2.305434</v>
       </c>
       <c r="K27" t="n">
-        <v>2.455159</v>
+        <v>2.455108</v>
       </c>
       <c r="L27" t="n">
-        <v>2.71049</v>
+        <v>2.710432</v>
       </c>
       <c r="M27" t="n">
-        <v>2.971907</v>
+        <v>2.971841</v>
       </c>
       <c r="N27" t="n">
-        <v>3.151243</v>
+        <v>3.15117</v>
       </c>
       <c r="O27" t="n">
-        <v>3.069279</v>
+        <v>3.069202</v>
       </c>
       <c r="P27" t="n">
-        <v>2.870329</v>
+        <v>2.870252</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.521266</v>
+        <v>2.521191</v>
       </c>
       <c r="R27" t="n">
-        <v>2.110941</v>
+        <v>2.110871</v>
       </c>
       <c r="S27" t="n">
-        <v>1.690589</v>
+        <v>1.690526</v>
       </c>
       <c r="T27" t="n">
-        <v>1.32183</v>
+        <v>1.321773</v>
       </c>
       <c r="U27" t="n">
-        <v>1.029191</v>
+        <v>1.029138</v>
       </c>
       <c r="V27" t="n">
-        <v>0.822817</v>
+        <v>0.8227640000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2502,58 +2502,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.408763</v>
+        <v>3.408771</v>
       </c>
       <c r="F28" t="n">
-        <v>4.331318</v>
+        <v>4.331335</v>
       </c>
       <c r="G28" t="n">
-        <v>5.117027</v>
+        <v>5.11707</v>
       </c>
       <c r="H28" t="n">
-        <v>6.433919</v>
+        <v>6.434005</v>
       </c>
       <c r="I28" t="n">
-        <v>7.983065</v>
+        <v>7.9832</v>
       </c>
       <c r="J28" t="n">
-        <v>9.476436</v>
+        <v>9.476615000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>11.236315</v>
+        <v>11.236538</v>
       </c>
       <c r="L28" t="n">
-        <v>13.455991</v>
+        <v>13.45626</v>
       </c>
       <c r="M28" t="n">
-        <v>15.762221</v>
+        <v>15.762535</v>
       </c>
       <c r="N28" t="n">
-        <v>17.682308</v>
+        <v>17.682656</v>
       </c>
       <c r="O28" t="n">
-        <v>18.12954</v>
+        <v>18.129895</v>
       </c>
       <c r="P28" t="n">
-        <v>17.783967</v>
+        <v>17.784315</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.322182</v>
+        <v>16.322508</v>
       </c>
       <c r="R28" t="n">
-        <v>14.205613</v>
+        <v>14.205906</v>
       </c>
       <c r="S28" t="n">
-        <v>11.755894</v>
+        <v>11.756151</v>
       </c>
       <c r="T28" t="n">
-        <v>9.446092999999999</v>
+        <v>9.446318</v>
       </c>
       <c r="U28" t="n">
-        <v>7.529377</v>
+        <v>7.529579</v>
       </c>
       <c r="V28" t="n">
-        <v>6.149638</v>
+        <v>6.149833</v>
       </c>
     </row>
     <row r="29">
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.39582</v>
+        <v>1.395825</v>
       </c>
       <c r="F29" t="n">
-        <v>1.782278</v>
+        <v>1.782287</v>
       </c>
       <c r="G29" t="n">
-        <v>1.999411</v>
+        <v>1.999422</v>
       </c>
       <c r="H29" t="n">
-        <v>2.297639</v>
+        <v>2.297654</v>
       </c>
       <c r="I29" t="n">
-        <v>2.623068</v>
+        <v>2.623095</v>
       </c>
       <c r="J29" t="n">
         <v>2.874017</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.938344</v>
+        <v>0.938324</v>
       </c>
       <c r="F30" t="n">
-        <v>1.132614</v>
+        <v>1.13255</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19814</v>
+        <v>1.198012</v>
       </c>
       <c r="H30" t="n">
-        <v>1.33617</v>
+        <v>1.335914</v>
       </c>
       <c r="I30" t="n">
-        <v>1.483379</v>
+        <v>1.482757</v>
       </c>
       <c r="J30" t="n">
         <v>5.315451</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.055648</v>
+        <v>0.05564</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07499500000000001</v>
+        <v>0.074971</v>
       </c>
       <c r="G31" t="n">
-        <v>0.084565</v>
+        <v>0.084523</v>
       </c>
       <c r="H31" t="n">
-        <v>0.097676</v>
+        <v>0.097596</v>
       </c>
       <c r="I31" t="n">
-        <v>0.112023</v>
+        <v>0.111839</v>
       </c>
       <c r="J31" t="n">
         <v>1.158873</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.706972</v>
+        <v>2.706979</v>
       </c>
       <c r="F32" t="n">
-        <v>3.165388</v>
+        <v>3.16539</v>
       </c>
       <c r="G32" t="n">
-        <v>3.267841</v>
+        <v>3.267829</v>
       </c>
       <c r="H32" t="n">
-        <v>3.592649</v>
+        <v>3.592617</v>
       </c>
       <c r="I32" t="n">
-        <v>4.039035</v>
+        <v>4.038969</v>
       </c>
       <c r="J32" t="n">
         <v>4.853433</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.205721</v>
+        <v>2.205717</v>
       </c>
       <c r="F33" t="n">
-        <v>2.795505</v>
+        <v>2.795488</v>
       </c>
       <c r="G33" t="n">
-        <v>3.111475</v>
+        <v>3.111441</v>
       </c>
       <c r="H33" t="n">
-        <v>3.568632</v>
+        <v>3.568567</v>
       </c>
       <c r="I33" t="n">
-        <v>4.042173</v>
+        <v>4.042023</v>
       </c>
       <c r="J33" t="n">
         <v>5.393046</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.839252</v>
+        <v>0.839122</v>
       </c>
       <c r="F34" t="n">
-        <v>1.868159</v>
+        <v>1.867806</v>
       </c>
       <c r="G34" t="n">
-        <v>3.530612</v>
+        <v>3.530003</v>
       </c>
       <c r="H34" t="n">
-        <v>5.855335</v>
+        <v>5.854303</v>
       </c>
       <c r="I34" t="n">
-        <v>8.32667</v>
+        <v>8.324498</v>
       </c>
       <c r="J34" t="n">
         <v>22.229247</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.381646</v>
+        <v>1.381661</v>
       </c>
       <c r="F35" t="n">
-        <v>2.15309</v>
+        <v>2.153144</v>
       </c>
       <c r="G35" t="n">
-        <v>2.866066</v>
+        <v>2.866189</v>
       </c>
       <c r="H35" t="n">
-        <v>3.605854</v>
+        <v>3.606113</v>
       </c>
       <c r="I35" t="n">
-        <v>4.162478</v>
+        <v>4.16309</v>
       </c>
       <c r="J35" t="n">
         <v>1.264978</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.188402</v>
+        <v>0.188405</v>
       </c>
       <c r="F36" t="n">
-        <v>0.236316</v>
+        <v>0.236322</v>
       </c>
       <c r="G36" t="n">
-        <v>0.23042</v>
+        <v>0.230429</v>
       </c>
       <c r="H36" t="n">
-        <v>0.224297</v>
+        <v>0.22431</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2165</v>
+        <v>0.216524</v>
       </c>
       <c r="J36" t="n">
         <v>0.10082</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.54749</v>
+        <v>1.547515</v>
       </c>
       <c r="F37" t="n">
-        <v>1.732983</v>
+        <v>1.733037</v>
       </c>
       <c r="G37" t="n">
-        <v>1.683484</v>
+        <v>1.683569</v>
       </c>
       <c r="H37" t="n">
-        <v>1.7096</v>
+        <v>1.709736</v>
       </c>
       <c r="I37" t="n">
-        <v>1.738472</v>
+        <v>1.738748</v>
       </c>
       <c r="J37" t="n">
         <v>0.403211</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.793939</v>
+        <v>3.793954</v>
       </c>
       <c r="F38" t="n">
-        <v>4.896097</v>
+        <v>4.896127</v>
       </c>
       <c r="G38" t="n">
-        <v>5.360207</v>
+        <v>5.360251</v>
       </c>
       <c r="H38" t="n">
-        <v>6.150166</v>
+        <v>6.150243</v>
       </c>
       <c r="I38" t="n">
-        <v>7.09849</v>
+        <v>7.098685</v>
       </c>
       <c r="J38" t="n">
         <v>6.953669</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.683734</v>
+        <v>0.683725</v>
       </c>
       <c r="F39" t="n">
-        <v>0.83908</v>
+        <v>0.839053</v>
       </c>
       <c r="G39" t="n">
-        <v>0.925756</v>
+        <v>0.925706</v>
       </c>
       <c r="H39" t="n">
-        <v>1.075473</v>
+        <v>1.075383</v>
       </c>
       <c r="I39" t="n">
-        <v>1.260051</v>
+        <v>1.259861</v>
       </c>
       <c r="J39" t="n">
         <v>2.451335</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.08637599999999999</v>
+        <v>0.08637400000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.111535</v>
+        <v>0.11153</v>
       </c>
       <c r="G40" t="n">
-        <v>0.124092</v>
+        <v>0.124083</v>
       </c>
       <c r="H40" t="n">
-        <v>0.140142</v>
+        <v>0.140125</v>
       </c>
       <c r="I40" t="n">
-        <v>0.158138</v>
+        <v>0.158099</v>
       </c>
       <c r="J40" t="n">
         <v>0.394386</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.121191</v>
+        <v>0.121189</v>
       </c>
       <c r="F41" t="n">
-        <v>0.172108</v>
+        <v>0.172103</v>
       </c>
       <c r="G41" t="n">
-        <v>0.19657</v>
+        <v>0.196561</v>
       </c>
       <c r="H41" t="n">
-        <v>0.224929</v>
+        <v>0.224912</v>
       </c>
       <c r="I41" t="n">
-        <v>0.247956</v>
+        <v>0.247916</v>
       </c>
       <c r="J41" t="n">
         <v>0.50951</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.29921</v>
+        <v>1.299232</v>
       </c>
       <c r="F42" t="n">
-        <v>1.519747</v>
+        <v>1.519798</v>
       </c>
       <c r="G42" t="n">
-        <v>1.463047</v>
+        <v>1.463126</v>
       </c>
       <c r="H42" t="n">
-        <v>1.448085</v>
+        <v>1.44821</v>
       </c>
       <c r="I42" t="n">
-        <v>1.454642</v>
+        <v>1.454891</v>
       </c>
       <c r="J42" t="n">
         <v>0.238961</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.293999</v>
+        <v>0.293995</v>
       </c>
       <c r="F43" t="n">
-        <v>0.51412</v>
+        <v>0.514111</v>
       </c>
       <c r="G43" t="n">
-        <v>0.72201</v>
+        <v>0.721998</v>
       </c>
       <c r="H43" t="n">
-        <v>0.96428</v>
+        <v>0.964265</v>
       </c>
       <c r="I43" t="n">
-        <v>1.218864</v>
+        <v>1.218842</v>
       </c>
       <c r="J43" t="n">
         <v>1.565093</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.842139</v>
+        <v>0.84212</v>
       </c>
       <c r="F44" t="n">
-        <v>1.20487</v>
+        <v>1.204813</v>
       </c>
       <c r="G44" t="n">
-        <v>1.418109</v>
+        <v>1.418001</v>
       </c>
       <c r="H44" t="n">
-        <v>1.72506</v>
+        <v>1.724856</v>
       </c>
       <c r="I44" t="n">
-        <v>2.099127</v>
+        <v>2.098659</v>
       </c>
       <c r="J44" t="n">
         <v>5.137659</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.65761</v>
+        <v>0.6576149999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.861969</v>
+        <v>0.8619790000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>0.951588</v>
+        <v>0.951605</v>
       </c>
       <c r="H45" t="n">
-        <v>1.070955</v>
+        <v>1.070985</v>
       </c>
       <c r="I45" t="n">
-        <v>1.177669</v>
+        <v>1.177732</v>
       </c>
       <c r="J45" t="n">
         <v>0.971679</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.521469</v>
+        <v>0.521443</v>
       </c>
       <c r="F46" t="n">
-        <v>0.766977</v>
+        <v>0.7669</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9607329999999999</v>
+        <v>0.960584</v>
       </c>
       <c r="H46" t="n">
-        <v>1.194694</v>
+        <v>1.1944</v>
       </c>
       <c r="I46" t="n">
-        <v>1.453625</v>
+        <v>1.452906</v>
       </c>
       <c r="J46" t="n">
         <v>6.022087</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>28.261619</v>
+        <v>28.261768</v>
       </c>
       <c r="F47" t="n">
-        <v>41.475774</v>
+        <v>41.476263</v>
       </c>
       <c r="G47" t="n">
-        <v>48.59589</v>
+        <v>48.596825</v>
       </c>
       <c r="H47" t="n">
-        <v>57.191363</v>
+        <v>57.193098</v>
       </c>
       <c r="I47" t="n">
-        <v>66.28484899999999</v>
+        <v>66.288799</v>
       </c>
       <c r="J47" t="n">
         <v>54.66082</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.214957</v>
+        <v>2.21497</v>
       </c>
       <c r="F48" t="n">
-        <v>2.938713</v>
+        <v>2.938744</v>
       </c>
       <c r="G48" t="n">
-        <v>3.307569</v>
+        <v>3.307624</v>
       </c>
       <c r="H48" t="n">
-        <v>3.711273</v>
+        <v>3.711367</v>
       </c>
       <c r="I48" t="n">
-        <v>4.072129</v>
+        <v>4.072321</v>
       </c>
       <c r="J48" t="n">
         <v>3.4942</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.243781</v>
+        <v>0.243772</v>
       </c>
       <c r="F49" t="n">
-        <v>0.34026</v>
+        <v>0.340236</v>
       </c>
       <c r="G49" t="n">
-        <v>0.392053</v>
+        <v>0.392008</v>
       </c>
       <c r="H49" t="n">
-        <v>0.450291</v>
+        <v>0.450204</v>
       </c>
       <c r="I49" t="n">
-        <v>0.506985</v>
+        <v>0.50678</v>
       </c>
       <c r="J49" t="n">
         <v>1.745264</v>
@@ -4177,16 +4177,16 @@
         <v>0.033521</v>
       </c>
       <c r="F50" t="n">
-        <v>0.041414</v>
+        <v>0.041415</v>
       </c>
       <c r="G50" t="n">
-        <v>0.040877</v>
+        <v>0.040878</v>
       </c>
       <c r="H50" t="n">
-        <v>0.040416</v>
+        <v>0.040417</v>
       </c>
       <c r="I50" t="n">
-        <v>0.039736</v>
+        <v>0.039737</v>
       </c>
       <c r="J50" t="n">
         <v>0.035115</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.384987</v>
+        <v>0.384969</v>
       </c>
       <c r="F51" t="n">
-        <v>0.478971</v>
+        <v>0.478916</v>
       </c>
       <c r="G51" t="n">
-        <v>0.511507</v>
+        <v>0.511399</v>
       </c>
       <c r="H51" t="n">
-        <v>0.558586</v>
+        <v>0.558372</v>
       </c>
       <c r="I51" t="n">
-        <v>0.614713</v>
+        <v>0.6141990000000001</v>
       </c>
       <c r="J51" t="n">
         <v>3.672474</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.37123</v>
+        <v>0.371224</v>
       </c>
       <c r="F52" t="n">
-        <v>0.426342</v>
+        <v>0.426322</v>
       </c>
       <c r="G52" t="n">
-        <v>0.415893</v>
+        <v>0.415852</v>
       </c>
       <c r="H52" t="n">
-        <v>0.425571</v>
+        <v>0.425489</v>
       </c>
       <c r="I52" t="n">
-        <v>0.450842</v>
+        <v>0.450645</v>
       </c>
       <c r="J52" t="n">
         <v>1.619106</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>73.85316899999999</v>
+        <v>73.857489</v>
       </c>
       <c r="F54" t="n">
-        <v>82.005392</v>
+        <v>82.009411</v>
       </c>
       <c r="G54" t="n">
-        <v>79.22708</v>
+        <v>79.231185</v>
       </c>
       <c r="H54" t="n">
-        <v>70.956095</v>
+        <v>70.960048</v>
       </c>
       <c r="I54" t="n">
-        <v>60.821544</v>
+        <v>60.825104</v>
       </c>
       <c r="J54" t="n">
-        <v>51.720274</v>
+        <v>51.723339</v>
       </c>
       <c r="K54" t="n">
-        <v>43.420068</v>
+        <v>43.422594</v>
       </c>
       <c r="L54" t="n">
-        <v>37.162516</v>
+        <v>37.164584</v>
       </c>
       <c r="M54" t="n">
-        <v>32.854968</v>
+        <v>32.856695</v>
       </c>
       <c r="N54" t="n">
-        <v>29.048339</v>
+        <v>29.049773</v>
       </c>
       <c r="O54" t="n">
-        <v>23.521092</v>
+        <v>23.522189</v>
       </c>
       <c r="P54" t="n">
-        <v>12.558954</v>
+        <v>12.559506</v>
       </c>
       <c r="Q54" t="n">
-        <v>-3.873551</v>
+        <v>-3.873709</v>
       </c>
       <c r="R54" t="n">
-        <v>-22.509491</v>
+        <v>-22.510337</v>
       </c>
       <c r="S54" t="n">
-        <v>-40.848635</v>
+        <v>-40.850031</v>
       </c>
       <c r="T54" t="n">
-        <v>-55.745215</v>
+        <v>-55.746913</v>
       </c>
       <c r="U54" t="n">
-        <v>-66.280435</v>
+        <v>-66.28218699999999</v>
       </c>
       <c r="V54" t="n">
-        <v>-74.36322199999999</v>
+        <v>-74.364875</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>48.307255</v>
+        <v>48.302935</v>
       </c>
       <c r="F55" t="n">
-        <v>60.221714</v>
+        <v>60.217696</v>
       </c>
       <c r="G55" t="n">
-        <v>62.216603</v>
+        <v>62.212499</v>
       </c>
       <c r="H55" t="n">
-        <v>57.187432</v>
+        <v>57.183479</v>
       </c>
       <c r="I55" t="n">
-        <v>48.812645</v>
+        <v>48.809086</v>
       </c>
       <c r="J55" t="n">
-        <v>40.348127</v>
+        <v>40.345061</v>
       </c>
       <c r="K55" t="n">
-        <v>32.36821</v>
+        <v>32.365684</v>
       </c>
       <c r="L55" t="n">
-        <v>26.183172</v>
+        <v>26.181103</v>
       </c>
       <c r="M55" t="n">
-        <v>21.760426</v>
+        <v>21.758699</v>
       </c>
       <c r="N55" t="n">
-        <v>18.044318</v>
+        <v>18.042884</v>
       </c>
       <c r="O55" t="n">
-        <v>13.782074</v>
+        <v>13.780977</v>
       </c>
       <c r="P55" t="n">
-        <v>6.964287</v>
+        <v>6.963735</v>
       </c>
       <c r="Q55" t="n">
-        <v>-2.026866</v>
+        <v>-2.026708</v>
       </c>
       <c r="R55" t="n">
-        <v>-11.155182</v>
+        <v>-11.154336</v>
       </c>
       <c r="S55" t="n">
-        <v>-19.145347</v>
+        <v>-19.14395</v>
       </c>
       <c r="T55" t="n">
-        <v>-24.685488</v>
+        <v>-24.683791</v>
       </c>
       <c r="U55" t="n">
-        <v>-27.815958</v>
+        <v>-27.814206</v>
       </c>
       <c r="V55" t="n">
-        <v>-29.731288</v>
+        <v>-29.729636</v>
       </c>
     </row>
     <row r="56">
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.383762</v>
+        <v>0.386396</v>
       </c>
       <c r="F58" t="n">
-        <v>0.389891</v>
+        <v>0.394923</v>
       </c>
       <c r="G58" t="n">
-        <v>0.391318</v>
+        <v>0.398896</v>
       </c>
       <c r="H58" t="n">
-        <v>0.378253</v>
+        <v>0.388908</v>
       </c>
       <c r="I58" t="n">
-        <v>0.32851</v>
+        <v>0.344298</v>
       </c>
       <c r="J58" t="n">
         <v>0.069172</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.087742</v>
+        <v>0.08738600000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>0.099663</v>
+        <v>0.09897599999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1105</v>
+        <v>0.109611</v>
       </c>
       <c r="H59" t="n">
-        <v>0.115515</v>
+        <v>0.114223</v>
       </c>
       <c r="I59" t="n">
-        <v>0.11485</v>
+        <v>0.112601</v>
       </c>
       <c r="J59" t="n">
         <v>0.145391</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.24731</v>
+        <v>0.248853</v>
       </c>
       <c r="F60" t="n">
-        <v>0.205715</v>
+        <v>0.207824</v>
       </c>
       <c r="G60" t="n">
-        <v>0.173794</v>
+        <v>0.175955</v>
       </c>
       <c r="H60" t="n">
-        <v>0.153317</v>
+        <v>0.155523</v>
       </c>
       <c r="I60" t="n">
-        <v>0.132906</v>
+        <v>0.135575</v>
       </c>
       <c r="J60" t="n">
         <v>0.083449</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.694802</v>
+        <v>2.704167</v>
       </c>
       <c r="F61" t="n">
-        <v>2.864522</v>
+        <v>2.882062</v>
       </c>
       <c r="G61" t="n">
-        <v>2.89896</v>
+        <v>2.921975</v>
       </c>
       <c r="H61" t="n">
-        <v>2.832795</v>
+        <v>2.858452</v>
       </c>
       <c r="I61" t="n">
-        <v>2.611437</v>
+        <v>2.638584</v>
       </c>
       <c r="J61" t="n">
         <v>2.140409</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10.144636</v>
+        <v>10.200771</v>
       </c>
       <c r="F62" t="n">
-        <v>10.93338</v>
+        <v>11.054406</v>
       </c>
       <c r="G62" t="n">
-        <v>10.89881</v>
+        <v>11.083585</v>
       </c>
       <c r="H62" t="n">
-        <v>10.171749</v>
+        <v>10.422013</v>
       </c>
       <c r="I62" t="n">
-        <v>8.482044</v>
+        <v>8.830522999999999</v>
       </c>
       <c r="J62" t="n">
         <v>2.58157</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8.241633999999999</v>
+        <v>8.280222</v>
       </c>
       <c r="F63" t="n">
-        <v>8.858573</v>
+        <v>8.937677000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>8.892156</v>
+        <v>9.006269</v>
       </c>
       <c r="H63" t="n">
-        <v>8.650164999999999</v>
+        <v>8.803595</v>
       </c>
       <c r="I63" t="n">
-        <v>7.801571</v>
+        <v>8.023605999999999</v>
       </c>
       <c r="J63" t="n">
         <v>3.96192</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.040866</v>
+        <v>0.040928</v>
       </c>
       <c r="F64" t="n">
-        <v>0.038401</v>
+        <v>0.038404</v>
       </c>
       <c r="G64" t="n">
-        <v>0.037012</v>
+        <v>0.036926</v>
       </c>
       <c r="H64" t="n">
-        <v>0.03582</v>
+        <v>0.035618</v>
       </c>
       <c r="I64" t="n">
-        <v>0.033944</v>
+        <v>0.033572</v>
       </c>
       <c r="J64" t="n">
         <v>0.036843</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6.017231</v>
+        <v>6.002561</v>
       </c>
       <c r="F65" t="n">
-        <v>7.076756</v>
+        <v>7.055584</v>
       </c>
       <c r="G65" t="n">
-        <v>7.909733</v>
+        <v>7.886857</v>
       </c>
       <c r="H65" t="n">
-        <v>8.411008000000001</v>
+        <v>8.381785000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>8.418447</v>
+        <v>8.371109000000001</v>
       </c>
       <c r="J65" t="n">
         <v>8.763934000000001</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.781167</v>
+        <v>3.758601</v>
       </c>
       <c r="F66" t="n">
-        <v>4.458734</v>
+        <v>4.419438</v>
       </c>
       <c r="G66" t="n">
-        <v>5.033625</v>
+        <v>4.982569</v>
       </c>
       <c r="H66" t="n">
-        <v>5.440847</v>
+        <v>5.376014</v>
       </c>
       <c r="I66" t="n">
-        <v>5.591388</v>
+        <v>5.50185</v>
       </c>
       <c r="J66" t="n">
         <v>6.528935</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1.770293</v>
+        <v>1.623655</v>
       </c>
       <c r="F67" t="n">
-        <v>2.487051</v>
+        <v>2.212098</v>
       </c>
       <c r="G67" t="n">
-        <v>3.182004</v>
+        <v>2.804466</v>
       </c>
       <c r="H67" t="n">
-        <v>3.918336</v>
+        <v>3.435923</v>
       </c>
       <c r="I67" t="n">
-        <v>5.010818</v>
+        <v>4.351414</v>
       </c>
       <c r="J67" t="n">
         <v>13.491601</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.443615</v>
+        <v>2.454621</v>
       </c>
       <c r="F68" t="n">
-        <v>2.727237</v>
+        <v>2.752991</v>
       </c>
       <c r="G68" t="n">
-        <v>3.061624</v>
+        <v>3.110759</v>
       </c>
       <c r="H68" t="n">
-        <v>3.200764</v>
+        <v>3.281269</v>
       </c>
       <c r="I68" t="n">
-        <v>2.880637</v>
+        <v>3.00871</v>
       </c>
       <c r="J68" t="n">
         <v>0.717826</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.06356100000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06582</v>
+        <v>0.065979</v>
       </c>
       <c r="G69" t="n">
-        <v>0.06626600000000001</v>
+        <v>0.066413</v>
       </c>
       <c r="H69" t="n">
-        <v>0.064834</v>
+        <v>0.064875</v>
       </c>
       <c r="I69" t="n">
-        <v>0.060693</v>
+        <v>0.060473</v>
       </c>
       <c r="J69" t="n">
         <v>0.06079</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.103001</v>
+        <v>2.055752</v>
       </c>
       <c r="F70" t="n">
-        <v>2.481939</v>
+        <v>2.390895</v>
       </c>
       <c r="G70" t="n">
-        <v>2.842392</v>
+        <v>2.713429</v>
       </c>
       <c r="H70" t="n">
-        <v>3.177634</v>
+        <v>3.008501</v>
       </c>
       <c r="I70" t="n">
-        <v>3.539204</v>
+        <v>3.306509</v>
       </c>
       <c r="J70" t="n">
         <v>6.391</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.659122</v>
+        <v>3.679251</v>
       </c>
       <c r="F71" t="n">
-        <v>4.173419</v>
+        <v>4.219002</v>
       </c>
       <c r="G71" t="n">
-        <v>4.253063</v>
+        <v>4.321854</v>
       </c>
       <c r="H71" t="n">
-        <v>4.043747</v>
+        <v>4.13416</v>
       </c>
       <c r="I71" t="n">
-        <v>3.530149</v>
+        <v>3.655587</v>
       </c>
       <c r="J71" t="n">
         <v>1.458003</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.572911</v>
+        <v>2.567089</v>
       </c>
       <c r="F72" t="n">
-        <v>2.627892</v>
+        <v>2.613252</v>
       </c>
       <c r="G72" t="n">
-        <v>2.657862</v>
+        <v>2.634034</v>
       </c>
       <c r="H72" t="n">
-        <v>2.65503</v>
+        <v>2.621052</v>
       </c>
       <c r="I72" t="n">
-        <v>2.579029</v>
+        <v>2.529803</v>
       </c>
       <c r="J72" t="n">
         <v>2.963984</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>12.531372</v>
+        <v>12.62915</v>
       </c>
       <c r="F73" t="n">
-        <v>9.794884</v>
+        <v>9.940315999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>7.003215</v>
+        <v>7.158599</v>
       </c>
       <c r="H73" t="n">
-        <v>5.239244</v>
+        <v>5.407002</v>
       </c>
       <c r="I73" t="n">
-        <v>3.852806</v>
+        <v>4.064139</v>
       </c>
       <c r="J73" t="n">
         <v>0.387996</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.033527</v>
+        <v>0.033476</v>
       </c>
       <c r="F74" t="n">
-        <v>0.039732</v>
+        <v>0.03978</v>
       </c>
       <c r="G74" t="n">
-        <v>0.041433</v>
+        <v>0.041568</v>
       </c>
       <c r="H74" t="n">
-        <v>0.039993</v>
+        <v>0.040138</v>
       </c>
       <c r="I74" t="n">
-        <v>0.036139</v>
+        <v>0.036219</v>
       </c>
       <c r="J74" t="n">
         <v>0.032585</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.865007</v>
+        <v>1.837573</v>
       </c>
       <c r="F75" t="n">
-        <v>1.992229</v>
+        <v>1.95778</v>
       </c>
       <c r="G75" t="n">
-        <v>2.007029</v>
+        <v>1.972026</v>
       </c>
       <c r="H75" t="n">
-        <v>1.762992</v>
+        <v>1.723988</v>
       </c>
       <c r="I75" t="n">
-        <v>1.563405</v>
+        <v>1.501429</v>
       </c>
       <c r="J75" t="n">
         <v>3.624666</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10.855982</v>
+        <v>10.922478</v>
       </c>
       <c r="F76" t="n">
-        <v>11.721169</v>
+        <v>11.77351</v>
       </c>
       <c r="G76" t="n">
-        <v>9.65875</v>
+        <v>9.645053000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>7.258514</v>
+        <v>7.186102</v>
       </c>
       <c r="I76" t="n">
-        <v>5.962456</v>
+        <v>5.792907</v>
       </c>
       <c r="J76" t="n">
         <v>12.244624</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.465203</v>
+        <v>3.440173</v>
       </c>
       <c r="F77" t="n">
-        <v>4.137261</v>
+        <v>4.119806</v>
       </c>
       <c r="G77" t="n">
-        <v>4.343256</v>
+        <v>4.329991</v>
       </c>
       <c r="H77" t="n">
-        <v>3.664345</v>
+        <v>3.645427</v>
       </c>
       <c r="I77" t="n">
-        <v>2.932722</v>
+        <v>2.890131</v>
       </c>
       <c r="J77" t="n">
         <v>4.330505</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>63.826955</v>
+        <v>64.516615</v>
       </c>
       <c r="F78" t="n">
-        <v>58.70103</v>
+        <v>59.225542</v>
       </c>
       <c r="G78" t="n">
-        <v>49.849136</v>
+        <v>50.147462</v>
       </c>
       <c r="H78" t="n">
-        <v>38.81019</v>
+        <v>38.97561</v>
       </c>
       <c r="I78" t="n">
-        <v>31.470736</v>
+        <v>31.593888</v>
       </c>
       <c r="J78" t="n">
         <v>25.434841</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3.684267</v>
+        <v>3.533603</v>
       </c>
       <c r="F79" t="n">
-        <v>4.958715</v>
+        <v>4.828399</v>
       </c>
       <c r="G79" t="n">
-        <v>6.393762</v>
+        <v>6.310982</v>
       </c>
       <c r="H79" t="n">
-        <v>6.821203</v>
+        <v>6.765616</v>
       </c>
       <c r="I79" t="n">
-        <v>6.666348</v>
+        <v>6.610133</v>
       </c>
       <c r="J79" t="n">
         <v>7.808074</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5.823075</v>
+        <v>5.797638</v>
       </c>
       <c r="F80" t="n">
-        <v>5.527055</v>
+        <v>5.444551</v>
       </c>
       <c r="G80" t="n">
-        <v>5.123119</v>
+        <v>4.997348</v>
       </c>
       <c r="H80" t="n">
-        <v>4.555114</v>
+        <v>4.395065</v>
       </c>
       <c r="I80" t="n">
-        <v>4.423628</v>
+        <v>4.169916</v>
       </c>
       <c r="J80" t="n">
         <v>12.844883</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2.277391</v>
+        <v>2.02531</v>
       </c>
       <c r="F81" t="n">
-        <v>2.927948</v>
+        <v>2.697232</v>
       </c>
       <c r="G81" t="n">
-        <v>3.558191</v>
+        <v>3.38155</v>
       </c>
       <c r="H81" t="n">
-        <v>3.728685</v>
+        <v>3.573964</v>
       </c>
       <c r="I81" t="n">
-        <v>3.798961</v>
+        <v>3.593188</v>
       </c>
       <c r="J81" t="n">
         <v>10.295737</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>20.437019</v>
+        <v>20.629412</v>
       </c>
       <c r="F82" t="n">
-        <v>21.909407</v>
+        <v>22.089425</v>
       </c>
       <c r="G82" t="n">
-        <v>21.583231</v>
+        <v>21.724509</v>
       </c>
       <c r="H82" t="n">
-        <v>18.854898</v>
+        <v>18.985251</v>
       </c>
       <c r="I82" t="n">
-        <v>16.210109</v>
+        <v>16.399064</v>
       </c>
       <c r="J82" t="n">
         <v>7.868962</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>35.469119</v>
+        <v>35.001216</v>
       </c>
       <c r="F83" t="n">
-        <v>49.89137</v>
+        <v>49.629938</v>
       </c>
       <c r="G83" t="n">
-        <v>64.9207</v>
+        <v>64.928251</v>
       </c>
       <c r="H83" t="n">
-        <v>68.094945</v>
+        <v>68.299863</v>
       </c>
       <c r="I83" t="n">
-        <v>63.997082</v>
+        <v>64.47479</v>
       </c>
       <c r="J83" t="n">
         <v>40.031391</v>
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>15.31171</v>
+        <v>14.720367</v>
       </c>
       <c r="F86" t="n">
-        <v>16.819259</v>
+        <v>16.106196</v>
       </c>
       <c r="G86" t="n">
-        <v>16.81966</v>
+        <v>16.092278</v>
       </c>
       <c r="H86" t="n">
-        <v>15.323237</v>
+        <v>14.667176</v>
       </c>
       <c r="I86" t="n">
-        <v>13.083927</v>
+        <v>12.528598</v>
       </c>
       <c r="J86" t="n">
-        <v>11.099457</v>
+        <v>10.629608</v>
       </c>
       <c r="K86" t="n">
-        <v>9.038729</v>
+        <v>8.655621999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>7.331087</v>
+        <v>7.017324</v>
       </c>
       <c r="M86" t="n">
-        <v>6.06865</v>
+        <v>5.797798</v>
       </c>
       <c r="N86" t="n">
-        <v>5.11977</v>
+        <v>4.870309</v>
       </c>
       <c r="O86" t="n">
-        <v>4.313931</v>
+        <v>4.081266</v>
       </c>
       <c r="P86" t="n">
-        <v>3.762249</v>
+        <v>3.541953</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.249467</v>
+        <v>3.049518</v>
       </c>
       <c r="R86" t="n">
-        <v>2.725733</v>
+        <v>2.554514</v>
       </c>
       <c r="S86" t="n">
-        <v>2.195896</v>
+        <v>2.057833</v>
       </c>
       <c r="T86" t="n">
-        <v>1.692723</v>
+        <v>1.587659</v>
       </c>
       <c r="U86" t="n">
-        <v>1.27347</v>
+        <v>1.195648</v>
       </c>
       <c r="V86" t="n">
-        <v>0.93881</v>
+        <v>0.8818550000000001</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.745741</v>
+        <v>1.788993</v>
       </c>
       <c r="F87" t="n">
-        <v>2.016546</v>
+        <v>2.091605</v>
       </c>
       <c r="G87" t="n">
-        <v>2.160144</v>
+        <v>2.276282</v>
       </c>
       <c r="H87" t="n">
-        <v>2.087885</v>
+        <v>2.226401</v>
       </c>
       <c r="I87" t="n">
-        <v>1.869956</v>
+        <v>2.010055</v>
       </c>
       <c r="J87" t="n">
-        <v>1.651152</v>
+        <v>1.784733</v>
       </c>
       <c r="K87" t="n">
-        <v>1.393712</v>
+        <v>1.512227</v>
       </c>
       <c r="L87" t="n">
-        <v>1.167564</v>
+        <v>1.270446</v>
       </c>
       <c r="M87" t="n">
-        <v>0.994336</v>
+        <v>1.083724</v>
       </c>
       <c r="N87" t="n">
-        <v>0.859101</v>
+        <v>0.936453</v>
       </c>
       <c r="O87" t="n">
-        <v>0.73908</v>
+        <v>0.804427</v>
       </c>
       <c r="P87" t="n">
-        <v>0.656981</v>
+        <v>0.71302</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.575599</v>
+        <v>0.622759</v>
       </c>
       <c r="R87" t="n">
-        <v>0.486565</v>
+        <v>0.5248429999999999</v>
       </c>
       <c r="S87" t="n">
-        <v>0.391337</v>
+        <v>0.420967</v>
       </c>
       <c r="T87" t="n">
-        <v>0.298423</v>
+        <v>0.320134</v>
       </c>
       <c r="U87" t="n">
-        <v>0.220343</v>
+        <v>0.235677</v>
       </c>
       <c r="V87" t="n">
-        <v>0.158044</v>
+        <v>0.168444</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24.065378</v>
+        <v>25.96466</v>
       </c>
       <c r="F88" t="n">
-        <v>24.079276</v>
+        <v>25.490339</v>
       </c>
       <c r="G88" t="n">
-        <v>24.09461</v>
+        <v>24.688313</v>
       </c>
       <c r="H88" t="n">
-        <v>22.658311</v>
+        <v>22.729246</v>
       </c>
       <c r="I88" t="n">
-        <v>20.007426</v>
+        <v>19.891771</v>
       </c>
       <c r="J88" t="n">
-        <v>17.516616</v>
+        <v>17.386607</v>
       </c>
       <c r="K88" t="n">
-        <v>14.73924</v>
+        <v>14.636959</v>
       </c>
       <c r="L88" t="n">
-        <v>12.36937</v>
+        <v>12.291986</v>
       </c>
       <c r="M88" t="n">
-        <v>10.575869</v>
+        <v>10.518677</v>
       </c>
       <c r="N88" t="n">
-        <v>9.176392999999999</v>
+        <v>9.140518999999999</v>
       </c>
       <c r="O88" t="n">
-        <v>7.928794</v>
+        <v>7.91473</v>
       </c>
       <c r="P88" t="n">
-        <v>7.09611</v>
+        <v>7.098115</v>
       </c>
       <c r="Q88" t="n">
-        <v>6.299459</v>
+        <v>6.312664</v>
       </c>
       <c r="R88" t="n">
-        <v>5.432318</v>
+        <v>5.452963</v>
       </c>
       <c r="S88" t="n">
-        <v>4.497973</v>
+        <v>4.520341</v>
       </c>
       <c r="T88" t="n">
-        <v>3.572777</v>
+        <v>3.595169</v>
       </c>
       <c r="U88" t="n">
-        <v>2.770334</v>
+        <v>2.793409</v>
       </c>
       <c r="V88" t="n">
-        <v>2.096244</v>
+        <v>2.1189</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.455203</v>
+        <v>4.801552</v>
       </c>
       <c r="F89" t="n">
-        <v>4.494236</v>
+        <v>4.844673</v>
       </c>
       <c r="G89" t="n">
-        <v>4.435542</v>
+        <v>4.775352</v>
       </c>
       <c r="H89" t="n">
-        <v>4.029597</v>
+        <v>4.338977</v>
       </c>
       <c r="I89" t="n">
-        <v>3.43883</v>
+        <v>3.70352</v>
       </c>
       <c r="J89" t="n">
-        <v>2.924839</v>
+        <v>3.145356</v>
       </c>
       <c r="K89" t="n">
-        <v>2.399894</v>
+        <v>2.573119</v>
       </c>
       <c r="L89" t="n">
-        <v>1.969162</v>
+        <v>2.105318</v>
       </c>
       <c r="M89" t="n">
-        <v>1.652504</v>
+        <v>1.764858</v>
       </c>
       <c r="N89" t="n">
-        <v>1.414622</v>
+        <v>1.511942</v>
       </c>
       <c r="O89" t="n">
-        <v>1.214384</v>
+        <v>1.29996</v>
       </c>
       <c r="P89" t="n">
-        <v>1.085489</v>
+        <v>1.163804</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.966654</v>
+        <v>1.038146</v>
       </c>
       <c r="R89" t="n">
-        <v>0.838809</v>
+        <v>0.902894</v>
       </c>
       <c r="S89" t="n">
-        <v>0.6973200000000001</v>
+        <v>0.753428</v>
       </c>
       <c r="T89" t="n">
-        <v>0.554111</v>
+        <v>0.60143</v>
       </c>
       <c r="U89" t="n">
-        <v>0.428839</v>
+        <v>0.467595</v>
       </c>
       <c r="V89" t="n">
-        <v>0.323324</v>
+        <v>0.354114</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>14.007799</v>
+        <v>13.648875</v>
       </c>
       <c r="F90" t="n">
-        <v>15.685778</v>
+        <v>14.976934</v>
       </c>
       <c r="G90" t="n">
-        <v>15.990187</v>
+        <v>15.250359</v>
       </c>
       <c r="H90" t="n">
-        <v>14.767033</v>
+        <v>14.152543</v>
       </c>
       <c r="I90" t="n">
-        <v>12.728835</v>
+        <v>12.263389</v>
       </c>
       <c r="J90" t="n">
-        <v>10.892142</v>
+        <v>10.527041</v>
       </c>
       <c r="K90" t="n">
-        <v>8.951866000000001</v>
+        <v>8.671226000000001</v>
       </c>
       <c r="L90" t="n">
-        <v>7.332136</v>
+        <v>7.118168</v>
       </c>
       <c r="M90" t="n">
-        <v>6.122587</v>
+        <v>5.958916</v>
       </c>
       <c r="N90" t="n">
-        <v>5.200992</v>
+        <v>5.072435</v>
       </c>
       <c r="O90" t="n">
-        <v>4.413287</v>
+        <v>4.310182</v>
       </c>
       <c r="P90" t="n">
-        <v>3.88533</v>
+        <v>3.797368</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.402389</v>
+        <v>3.326576</v>
       </c>
       <c r="R90" t="n">
-        <v>2.907919</v>
+        <v>2.843366</v>
       </c>
       <c r="S90" t="n">
-        <v>2.392835</v>
+        <v>2.340061</v>
       </c>
       <c r="T90" t="n">
-        <v>1.88678</v>
+        <v>1.846583</v>
       </c>
       <c r="U90" t="n">
-        <v>1.4552</v>
+        <v>1.425332</v>
       </c>
       <c r="V90" t="n">
-        <v>1.10133</v>
+        <v>1.078817</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4.374061</v>
+        <v>4.149923</v>
       </c>
       <c r="F91" t="n">
-        <v>4.886429</v>
+        <v>4.594512</v>
       </c>
       <c r="G91" t="n">
-        <v>4.912659</v>
+        <v>4.613675</v>
       </c>
       <c r="H91" t="n">
-        <v>4.492274</v>
+        <v>4.199904</v>
       </c>
       <c r="I91" t="n">
-        <v>3.853774</v>
+        <v>3.573047</v>
       </c>
       <c r="J91" t="n">
-        <v>3.294504</v>
+        <v>3.02207</v>
       </c>
       <c r="K91" t="n">
-        <v>2.710049</v>
+        <v>2.459405</v>
       </c>
       <c r="L91" t="n">
-        <v>2.214936</v>
+        <v>1.992833</v>
       </c>
       <c r="M91" t="n">
-        <v>1.829231</v>
+        <v>1.637271</v>
       </c>
       <c r="N91" t="n">
-        <v>1.517754</v>
+        <v>1.356269</v>
       </c>
       <c r="O91" t="n">
-        <v>1.249419</v>
+        <v>1.11698</v>
       </c>
       <c r="P91" t="n">
-        <v>1.065067</v>
+        <v>0.953494</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.903809</v>
+        <v>0.8105830000000001</v>
       </c>
       <c r="R91" t="n">
-        <v>0.749004</v>
+        <v>0.673177</v>
       </c>
       <c r="S91" t="n">
-        <v>0.595387</v>
+        <v>0.53698</v>
       </c>
       <c r="T91" t="n">
-        <v>0.453604</v>
+        <v>0.410784</v>
       </c>
       <c r="U91" t="n">
-        <v>0.339538</v>
+        <v>0.308623</v>
       </c>
       <c r="V91" t="n">
-        <v>0.251098</v>
+        <v>0.22897</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.890533</v>
+        <v>2.61205</v>
       </c>
       <c r="F92" t="n">
-        <v>3.283831</v>
+        <v>2.949767</v>
       </c>
       <c r="G92" t="n">
-        <v>3.258687</v>
+        <v>2.962666</v>
       </c>
       <c r="H92" t="n">
-        <v>2.952531</v>
+        <v>2.701354</v>
       </c>
       <c r="I92" t="n">
-        <v>2.525052</v>
+        <v>2.308958</v>
       </c>
       <c r="J92" t="n">
-        <v>2.160805</v>
+        <v>1.965709</v>
       </c>
       <c r="K92" t="n">
-        <v>1.780132</v>
+        <v>1.608781</v>
       </c>
       <c r="L92" t="n">
-        <v>1.458726</v>
+        <v>1.31052</v>
       </c>
       <c r="M92" t="n">
-        <v>1.209582</v>
+        <v>1.08323</v>
       </c>
       <c r="N92" t="n">
-        <v>1.011437</v>
+        <v>0.905</v>
       </c>
       <c r="O92" t="n">
-        <v>0.83957</v>
+        <v>0.751485</v>
       </c>
       <c r="P92" t="n">
-        <v>0.720796</v>
+        <v>0.645717</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.614002</v>
+        <v>0.550844</v>
       </c>
       <c r="R92" t="n">
-        <v>0.509115</v>
+        <v>0.457662</v>
       </c>
       <c r="S92" t="n">
-        <v>0.405098</v>
+        <v>0.365213</v>
       </c>
       <c r="T92" t="n">
-        <v>0.308615</v>
+        <v>0.27913</v>
       </c>
       <c r="U92" t="n">
-        <v>0.230904</v>
+        <v>0.209334</v>
       </c>
       <c r="V92" t="n">
-        <v>0.170147</v>
+        <v>0.154603</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.45542</v>
+        <v>0.45572</v>
       </c>
       <c r="F93" t="n">
-        <v>0.511409</v>
+        <v>0.51281</v>
       </c>
       <c r="G93" t="n">
-        <v>0.527487</v>
+        <v>0.537207</v>
       </c>
       <c r="H93" t="n">
-        <v>0.493318</v>
+        <v>0.512223</v>
       </c>
       <c r="I93" t="n">
-        <v>0.429396</v>
+        <v>0.453813</v>
       </c>
       <c r="J93" t="n">
-        <v>0.368596</v>
+        <v>0.39502</v>
       </c>
       <c r="K93" t="n">
-        <v>0.302136</v>
+        <v>0.326952</v>
       </c>
       <c r="L93" t="n">
-        <v>0.245762</v>
+        <v>0.267585</v>
       </c>
       <c r="M93" t="n">
-        <v>0.203507</v>
+        <v>0.222103</v>
       </c>
       <c r="N93" t="n">
-        <v>0.171381</v>
+        <v>0.186856</v>
       </c>
       <c r="O93" t="n">
-        <v>0.144256</v>
+        <v>0.156728</v>
       </c>
       <c r="P93" t="n">
-        <v>0.125913</v>
+        <v>0.136146</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.108605</v>
+        <v>0.116938</v>
       </c>
       <c r="R93" t="n">
-        <v>0.090558</v>
+        <v>0.097145</v>
       </c>
       <c r="S93" t="n">
-        <v>0.07203900000000001</v>
+        <v>0.076987</v>
       </c>
       <c r="T93" t="n">
-        <v>0.05452</v>
+        <v>0.058031</v>
       </c>
       <c r="U93" t="n">
-        <v>0.04004</v>
+        <v>0.042435</v>
       </c>
       <c r="V93" t="n">
-        <v>0.028643</v>
+        <v>0.030212</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>74.707846</v>
+        <v>77.729893</v>
       </c>
       <c r="F94" t="n">
-        <v>81.14323400000001</v>
+        <v>85.553754</v>
       </c>
       <c r="G94" t="n">
-        <v>81.770535</v>
+        <v>86.604257</v>
       </c>
       <c r="H94" t="n">
-        <v>74.788571</v>
+        <v>79.275488</v>
       </c>
       <c r="I94" t="n">
-        <v>63.702653</v>
+        <v>67.456552</v>
       </c>
       <c r="J94" t="n">
-        <v>53.822059</v>
+        <v>56.924144</v>
       </c>
       <c r="K94" t="n">
-        <v>43.751158</v>
+        <v>46.239111</v>
       </c>
       <c r="L94" t="n">
-        <v>35.514515</v>
+        <v>37.516833</v>
       </c>
       <c r="M94" t="n">
-        <v>29.454397</v>
+        <v>31.087509</v>
       </c>
       <c r="N94" t="n">
-        <v>24.88698</v>
+        <v>26.231202</v>
       </c>
       <c r="O94" t="n">
-        <v>21.044641</v>
+        <v>22.143546</v>
       </c>
       <c r="P94" t="n">
-        <v>18.478499</v>
+        <v>19.40703</v>
       </c>
       <c r="Q94" t="n">
-        <v>16.132082</v>
+        <v>16.908131</v>
       </c>
       <c r="R94" t="n">
-        <v>13.69251</v>
+        <v>14.320246</v>
       </c>
       <c r="S94" t="n">
-        <v>11.135354</v>
+        <v>11.620074</v>
       </c>
       <c r="T94" t="n">
-        <v>8.685074999999999</v>
+        <v>9.036923</v>
       </c>
       <c r="U94" t="n">
-        <v>6.6312</v>
+        <v>6.879686</v>
       </c>
       <c r="V94" t="n">
-        <v>4.962925</v>
+        <v>5.134799</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>34.489685</v>
+        <v>30.132735</v>
       </c>
       <c r="F95" t="n">
-        <v>38.850021</v>
+        <v>34.48382</v>
       </c>
       <c r="G95" t="n">
-        <v>38.143149</v>
+        <v>34.646512</v>
       </c>
       <c r="H95" t="n">
-        <v>34.145626</v>
+        <v>31.562773</v>
       </c>
       <c r="I95" t="n">
-        <v>28.729152</v>
+        <v>26.86413</v>
       </c>
       <c r="J95" t="n">
-        <v>24.043438</v>
+        <v>22.624228</v>
       </c>
       <c r="K95" t="n">
-        <v>19.304968</v>
+        <v>18.218537</v>
       </c>
       <c r="L95" t="n">
-        <v>15.40768</v>
+        <v>14.557175</v>
       </c>
       <c r="M95" t="n">
-        <v>12.483075</v>
+        <v>11.805662</v>
       </c>
       <c r="N95" t="n">
-        <v>10.232111</v>
+        <v>9.688304</v>
       </c>
       <c r="O95" t="n">
-        <v>8.347915</v>
+        <v>7.913384</v>
       </c>
       <c r="P95" t="n">
-        <v>7.045131</v>
+        <v>6.68692</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.903602</v>
+        <v>5.609188</v>
       </c>
       <c r="R95" t="n">
-        <v>4.821351</v>
+        <v>4.58511</v>
       </c>
       <c r="S95" t="n">
-        <v>3.792583</v>
+        <v>3.609463</v>
       </c>
       <c r="T95" t="n">
-        <v>2.853176</v>
+        <v>2.720044</v>
       </c>
       <c r="U95" t="n">
-        <v>2.101986</v>
+        <v>2.00601</v>
       </c>
       <c r="V95" t="n">
-        <v>1.518749</v>
+        <v>1.451251</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>8.539463</v>
+        <v>8.843616000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>9.167751000000001</v>
+        <v>9.269824</v>
       </c>
       <c r="G96" t="n">
-        <v>9.472412</v>
+        <v>9.235859</v>
       </c>
       <c r="H96" t="n">
-        <v>9.044109000000001</v>
+        <v>8.60249</v>
       </c>
       <c r="I96" t="n">
-        <v>8.024234999999999</v>
+        <v>7.539858</v>
       </c>
       <c r="J96" t="n">
-        <v>6.998449</v>
+        <v>6.551763</v>
       </c>
       <c r="K96" t="n">
-        <v>5.833327</v>
+        <v>5.45915</v>
       </c>
       <c r="L96" t="n">
-        <v>4.837055</v>
+        <v>4.529944</v>
       </c>
       <c r="M96" t="n">
-        <v>4.082277</v>
+        <v>3.826294</v>
       </c>
       <c r="N96" t="n">
-        <v>3.492157</v>
+        <v>3.277246</v>
       </c>
       <c r="O96" t="n">
-        <v>2.97163</v>
+        <v>2.793776</v>
       </c>
       <c r="P96" t="n">
-        <v>2.617227</v>
+        <v>2.465519</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.291309</v>
+        <v>2.162715</v>
       </c>
       <c r="R96" t="n">
-        <v>1.95732</v>
+        <v>1.850406</v>
       </c>
       <c r="S96" t="n">
-        <v>1.604472</v>
+        <v>1.519627</v>
       </c>
       <c r="T96" t="n">
-        <v>1.263395</v>
+        <v>1.198337</v>
       </c>
       <c r="U96" t="n">
-        <v>0.975083</v>
+        <v>0.926139</v>
       </c>
       <c r="V96" t="n">
-        <v>0.738988</v>
+        <v>0.702936</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3.340544</v>
+        <v>3.534999</v>
       </c>
       <c r="F97" t="n">
-        <v>3.43147</v>
+        <v>3.495005</v>
       </c>
       <c r="G97" t="n">
-        <v>3.549224</v>
+        <v>3.451536</v>
       </c>
       <c r="H97" t="n">
-        <v>3.42278</v>
+        <v>3.236696</v>
       </c>
       <c r="I97" t="n">
-        <v>3.07142</v>
+        <v>2.870966</v>
       </c>
       <c r="J97" t="n">
-        <v>2.714067</v>
+        <v>2.529846</v>
       </c>
       <c r="K97" t="n">
-        <v>2.294378</v>
+        <v>2.138499</v>
       </c>
       <c r="L97" t="n">
-        <v>1.92941</v>
+        <v>1.799272</v>
       </c>
       <c r="M97" t="n">
-        <v>1.650562</v>
+        <v>1.540536</v>
       </c>
       <c r="N97" t="n">
-        <v>1.432655</v>
+        <v>1.338817</v>
       </c>
       <c r="O97" t="n">
-        <v>1.240157</v>
+        <v>1.160599</v>
       </c>
       <c r="P97" t="n">
-        <v>1.114586</v>
+        <v>1.04429</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.993435</v>
+        <v>0.932351</v>
       </c>
       <c r="R97" t="n">
-        <v>0.860938</v>
+        <v>0.809813</v>
       </c>
       <c r="S97" t="n">
-        <v>0.716571</v>
+        <v>0.675891</v>
       </c>
       <c r="T97" t="n">
-        <v>0.572864</v>
+        <v>0.541839</v>
       </c>
       <c r="U97" t="n">
-        <v>0.447523</v>
+        <v>0.424571</v>
       </c>
       <c r="V97" t="n">
-        <v>0.34231</v>
+        <v>0.32571</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16.053263</v>
+        <v>16.19046</v>
       </c>
       <c r="F98" t="n">
-        <v>16.359694</v>
+        <v>16.428352</v>
       </c>
       <c r="G98" t="n">
-        <v>16.588334</v>
+        <v>16.568137</v>
       </c>
       <c r="H98" t="n">
-        <v>16.046417</v>
+        <v>15.961403</v>
       </c>
       <c r="I98" t="n">
-        <v>14.735008</v>
+        <v>14.614658</v>
       </c>
       <c r="J98" t="n">
-        <v>12.922946</v>
+        <v>12.792744</v>
       </c>
       <c r="K98" t="n">
-        <v>10.894791</v>
+        <v>10.770886</v>
       </c>
       <c r="L98" t="n">
-        <v>9.147224</v>
+        <v>9.034947000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>7.905316</v>
+        <v>7.803082</v>
       </c>
       <c r="N98" t="n">
-        <v>7.085987</v>
+        <v>6.990922</v>
       </c>
       <c r="O98" t="n">
-        <v>6.384953</v>
+        <v>6.29704</v>
       </c>
       <c r="P98" t="n">
-        <v>5.959438</v>
+        <v>5.875928</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.623109</v>
+        <v>5.543094</v>
       </c>
       <c r="R98" t="n">
-        <v>5.221434</v>
+        <v>5.146179</v>
       </c>
       <c r="S98" t="n">
-        <v>4.676151</v>
+        <v>4.608134</v>
       </c>
       <c r="T98" t="n">
-        <v>4.051519</v>
+        <v>3.991982</v>
       </c>
       <c r="U98" t="n">
-        <v>3.447354</v>
+        <v>3.396235</v>
       </c>
       <c r="V98" t="n">
-        <v>2.910969</v>
+        <v>2.867489</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>22.938834</v>
+        <v>23.209875</v>
       </c>
       <c r="F99" t="n">
-        <v>22.114224</v>
+        <v>22.457096</v>
       </c>
       <c r="G99" t="n">
-        <v>20.719639</v>
+        <v>21.103575</v>
       </c>
       <c r="H99" t="n">
-        <v>18.886976</v>
+        <v>19.275038</v>
       </c>
       <c r="I99" t="n">
-        <v>16.776864</v>
+        <v>17.138889</v>
       </c>
       <c r="J99" t="n">
-        <v>14.538324</v>
+        <v>14.856204</v>
       </c>
       <c r="K99" t="n">
-        <v>12.265498</v>
+        <v>12.531439</v>
       </c>
       <c r="L99" t="n">
-        <v>10.387377</v>
+        <v>10.608154</v>
       </c>
       <c r="M99" t="n">
-        <v>9.11375</v>
+        <v>9.302592000000001</v>
       </c>
       <c r="N99" t="n">
-        <v>8.34042</v>
+        <v>8.508725999999999</v>
       </c>
       <c r="O99" t="n">
-        <v>7.723481</v>
+        <v>7.875317</v>
       </c>
       <c r="P99" t="n">
-        <v>7.438344</v>
+        <v>7.581341</v>
       </c>
       <c r="Q99" t="n">
-        <v>7.24605</v>
+        <v>7.382542</v>
       </c>
       <c r="R99" t="n">
-        <v>6.956837</v>
+        <v>7.085124</v>
       </c>
       <c r="S99" t="n">
-        <v>6.480854</v>
+        <v>6.597299</v>
       </c>
       <c r="T99" t="n">
-        <v>5.848312</v>
+        <v>5.950655</v>
       </c>
       <c r="U99" t="n">
-        <v>5.184097</v>
+        <v>5.272451</v>
       </c>
       <c r="V99" t="n">
-        <v>4.560172</v>
+        <v>4.635692</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>10.160396</v>
+        <v>10.14216</v>
       </c>
       <c r="F100" t="n">
-        <v>11.452073</v>
+        <v>11.375895</v>
       </c>
       <c r="G100" t="n">
-        <v>12.162743</v>
+        <v>12.033603</v>
       </c>
       <c r="H100" t="n">
-        <v>12.015669</v>
+        <v>11.854267</v>
       </c>
       <c r="I100" t="n">
-        <v>11.148679</v>
+        <v>10.976534</v>
       </c>
       <c r="J100" t="n">
-        <v>9.850132</v>
+        <v>9.684098000000001</v>
       </c>
       <c r="K100" t="n">
-        <v>8.357582000000001</v>
+        <v>8.208209999999999</v>
       </c>
       <c r="L100" t="n">
-        <v>7.080553</v>
+        <v>6.94843</v>
       </c>
       <c r="M100" t="n">
-        <v>6.197039</v>
+        <v>6.077369</v>
       </c>
       <c r="N100" t="n">
-        <v>5.637559</v>
+        <v>5.525784</v>
       </c>
       <c r="O100" t="n">
-        <v>5.169895</v>
+        <v>5.065349</v>
       </c>
       <c r="P100" t="n">
-        <v>4.925673</v>
+        <v>4.82481</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.74284</v>
+        <v>4.645101</v>
       </c>
       <c r="R100" t="n">
-        <v>4.488898</v>
+        <v>4.396185</v>
       </c>
       <c r="S100" t="n">
-        <v>4.120888</v>
+        <v>4.035323</v>
       </c>
       <c r="T100" t="n">
-        <v>3.669897</v>
+        <v>3.593189</v>
       </c>
       <c r="U100" t="n">
-        <v>3.205299</v>
+        <v>3.138032</v>
       </c>
       <c r="V100" t="n">
-        <v>2.77723</v>
+        <v>2.718716</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>11.588084</v>
+        <v>11.654496</v>
       </c>
       <c r="F101" t="n">
-        <v>11.795049</v>
+        <v>11.847634</v>
       </c>
       <c r="G101" t="n">
-        <v>11.475829</v>
+        <v>11.507823</v>
       </c>
       <c r="H101" t="n">
-        <v>10.647229</v>
+        <v>10.661228</v>
       </c>
       <c r="I101" t="n">
-        <v>9.498964000000001</v>
+        <v>9.499224</v>
       </c>
       <c r="J101" t="n">
-        <v>8.215674</v>
+        <v>8.206956</v>
       </c>
       <c r="K101" t="n">
-        <v>6.90875</v>
+        <v>6.894853</v>
       </c>
       <c r="L101" t="n">
-        <v>5.840584</v>
+        <v>5.823779</v>
       </c>
       <c r="M101" t="n">
-        <v>5.123427</v>
+        <v>5.104591</v>
       </c>
       <c r="N101" t="n">
-        <v>4.685993</v>
+        <v>4.665737</v>
       </c>
       <c r="O101" t="n">
-        <v>4.332367</v>
+        <v>4.311581</v>
       </c>
       <c r="P101" t="n">
-        <v>4.159659</v>
+        <v>4.138655</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.039849</v>
+        <v>4.018926</v>
       </c>
       <c r="R101" t="n">
-        <v>3.867165</v>
+        <v>3.846769</v>
       </c>
       <c r="S101" t="n">
-        <v>3.592462</v>
+        <v>3.572824</v>
       </c>
       <c r="T101" t="n">
-        <v>3.231107</v>
+        <v>3.212841</v>
       </c>
       <c r="U101" t="n">
-        <v>2.855112</v>
+        <v>2.838538</v>
       </c>
       <c r="V101" t="n">
-        <v>2.505787</v>
+        <v>2.490846</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>108.576272</v>
+        <v>107.999377</v>
       </c>
       <c r="F102" t="n">
-        <v>113.8122</v>
+        <v>113.428307</v>
       </c>
       <c r="G102" t="n">
-        <v>107.480631</v>
+        <v>107.328949</v>
       </c>
       <c r="H102" t="n">
-        <v>96.590047</v>
+        <v>96.60822899999999</v>
       </c>
       <c r="I102" t="n">
-        <v>84.31058899999999</v>
+        <v>84.42376400000001</v>
       </c>
       <c r="J102" t="n">
-        <v>72.006328</v>
+        <v>72.156668</v>
       </c>
       <c r="K102" t="n">
-        <v>60.078699</v>
+        <v>60.229795</v>
       </c>
       <c r="L102" t="n">
-        <v>50.452467</v>
+        <v>50.590248</v>
       </c>
       <c r="M102" t="n">
-        <v>43.990895</v>
+        <v>44.112037</v>
       </c>
       <c r="N102" t="n">
-        <v>40.07312</v>
+        <v>40.178685</v>
       </c>
       <c r="O102" t="n">
-        <v>36.883534</v>
+        <v>36.975351</v>
       </c>
       <c r="P102" t="n">
-        <v>35.362153</v>
+        <v>35.444108</v>
       </c>
       <c r="Q102" t="n">
-        <v>34.355495</v>
+        <v>34.428886</v>
       </c>
       <c r="R102" t="n">
-        <v>32.902648</v>
+        <v>32.967613</v>
       </c>
       <c r="S102" t="n">
-        <v>30.508379</v>
+        <v>30.564632</v>
       </c>
       <c r="T102" t="n">
-        <v>27.42631</v>
+        <v>27.472617</v>
       </c>
       <c r="U102" t="n">
-        <v>24.250595</v>
+        <v>24.287158</v>
       </c>
       <c r="V102" t="n">
-        <v>21.302647</v>
+        <v>21.330484</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>194.009464</v>
+        <v>195.314345</v>
       </c>
       <c r="F103" t="n">
-        <v>199.238952</v>
+        <v>199.487936</v>
       </c>
       <c r="G103" t="n">
-        <v>202.50321</v>
+        <v>201.613907</v>
       </c>
       <c r="H103" t="n">
-        <v>194.449371</v>
+        <v>192.836944</v>
       </c>
       <c r="I103" t="n">
-        <v>175.762388</v>
+        <v>173.864741</v>
       </c>
       <c r="J103" t="n">
-        <v>151.099697</v>
+        <v>149.23962</v>
       </c>
       <c r="K103" t="n">
-        <v>124.455826</v>
+        <v>122.817688</v>
       </c>
       <c r="L103" t="n">
-        <v>101.958377</v>
+        <v>100.572915</v>
       </c>
       <c r="M103" t="n">
-        <v>86.04351800000001</v>
+        <v>84.85915199999999</v>
       </c>
       <c r="N103" t="n">
-        <v>75.533135</v>
+        <v>74.490374</v>
       </c>
       <c r="O103" t="n">
-        <v>66.994392</v>
+        <v>66.071702</v>
       </c>
       <c r="P103" t="n">
-        <v>61.83532</v>
+        <v>60.9905</v>
       </c>
       <c r="Q103" t="n">
-        <v>57.714649</v>
+        <v>56.937672</v>
       </c>
       <c r="R103" t="n">
-        <v>53.037345</v>
+        <v>52.339213</v>
       </c>
       <c r="S103" t="n">
-        <v>47.103435</v>
+        <v>46.499562</v>
       </c>
       <c r="T103" t="n">
-        <v>40.499759</v>
+        <v>39.994394</v>
       </c>
       <c r="U103" t="n">
-        <v>34.258937</v>
+        <v>33.841948</v>
       </c>
       <c r="V103" t="n">
-        <v>28.783606</v>
+        <v>28.443381</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>22.758484</v>
+        <v>22.633309</v>
       </c>
       <c r="F104" t="n">
-        <v>23.298106</v>
+        <v>23.206362</v>
       </c>
       <c r="G104" t="n">
-        <v>21.545294</v>
+        <v>21.490378</v>
       </c>
       <c r="H104" t="n">
-        <v>18.744068</v>
+        <v>18.731141</v>
       </c>
       <c r="I104" t="n">
-        <v>15.817351</v>
+        <v>15.834865</v>
       </c>
       <c r="J104" t="n">
-        <v>13.08934</v>
+        <v>13.123754</v>
       </c>
       <c r="K104" t="n">
-        <v>10.61718</v>
+        <v>10.657276</v>
       </c>
       <c r="L104" t="n">
-        <v>8.688107</v>
+        <v>8.727874999999999</v>
       </c>
       <c r="M104" t="n">
-        <v>7.388017</v>
+        <v>7.425551</v>
       </c>
       <c r="N104" t="n">
-        <v>6.567409</v>
+        <v>6.602394</v>
       </c>
       <c r="O104" t="n">
-        <v>5.915192</v>
+        <v>5.946751</v>
       </c>
       <c r="P104" t="n">
-        <v>5.54017</v>
+        <v>5.569184</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.24808</v>
+        <v>5.274383</v>
       </c>
       <c r="R104" t="n">
-        <v>4.900207</v>
+        <v>4.923109</v>
       </c>
       <c r="S104" t="n">
-        <v>4.43082</v>
+        <v>4.449809</v>
       </c>
       <c r="T104" t="n">
-        <v>3.883183</v>
+        <v>3.898436</v>
       </c>
       <c r="U104" t="n">
-        <v>3.347735</v>
+        <v>3.359932</v>
       </c>
       <c r="V104" t="n">
-        <v>2.867998</v>
+        <v>2.877754</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>9.476673</v>
+        <v>9.531599999999999</v>
       </c>
       <c r="F105" t="n">
-        <v>9.951686</v>
+        <v>9.996043</v>
       </c>
       <c r="G105" t="n">
-        <v>9.789102</v>
+        <v>9.829397999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>9.161718</v>
+        <v>9.196735</v>
       </c>
       <c r="I105" t="n">
-        <v>8.295432</v>
+        <v>8.32213</v>
       </c>
       <c r="J105" t="n">
-        <v>7.331923</v>
+        <v>7.348106</v>
       </c>
       <c r="K105" t="n">
-        <v>6.308035</v>
+        <v>6.314787</v>
       </c>
       <c r="L105" t="n">
-        <v>5.431227</v>
+        <v>5.431545</v>
       </c>
       <c r="M105" t="n">
-        <v>4.819163</v>
+        <v>4.815745</v>
       </c>
       <c r="N105" t="n">
-        <v>4.439428</v>
+        <v>4.433722</v>
       </c>
       <c r="O105" t="n">
-        <v>4.127411</v>
+        <v>4.119952</v>
       </c>
       <c r="P105" t="n">
-        <v>3.99569</v>
+        <v>3.986234</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.906062</v>
+        <v>3.894742</v>
       </c>
       <c r="R105" t="n">
-        <v>3.756552</v>
+        <v>3.743614</v>
       </c>
       <c r="S105" t="n">
-        <v>3.501463</v>
+        <v>3.487205</v>
       </c>
       <c r="T105" t="n">
-        <v>3.154855</v>
+        <v>3.140266</v>
       </c>
       <c r="U105" t="n">
-        <v>2.788134</v>
+        <v>2.774006</v>
       </c>
       <c r="V105" t="n">
-        <v>2.443219</v>
+        <v>2.429825</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>120.489024</v>
+        <v>119.658852</v>
       </c>
       <c r="F106" t="n">
-        <v>121.095</v>
+        <v>120.707465</v>
       </c>
       <c r="G106" t="n">
-        <v>108.312559</v>
+        <v>108.419543</v>
       </c>
       <c r="H106" t="n">
-        <v>93.607889</v>
+        <v>94.006032</v>
       </c>
       <c r="I106" t="n">
-        <v>79.542159</v>
+        <v>80.053061</v>
       </c>
       <c r="J106" t="n">
-        <v>66.568162</v>
+        <v>67.07501000000001</v>
       </c>
       <c r="K106" t="n">
-        <v>54.551769</v>
+        <v>54.993774</v>
       </c>
       <c r="L106" t="n">
-        <v>45.006723</v>
+        <v>45.371671</v>
       </c>
       <c r="M106" t="n">
-        <v>38.497236</v>
+        <v>38.800069</v>
       </c>
       <c r="N106" t="n">
-        <v>34.332128</v>
+        <v>34.589935</v>
       </c>
       <c r="O106" t="n">
-        <v>30.876576</v>
+        <v>31.097377</v>
       </c>
       <c r="P106" t="n">
-        <v>28.835665</v>
+        <v>29.030888</v>
       </c>
       <c r="Q106" t="n">
-        <v>27.252188</v>
+        <v>27.424201</v>
       </c>
       <c r="R106" t="n">
-        <v>25.404919</v>
+        <v>25.552386</v>
       </c>
       <c r="S106" t="n">
-        <v>22.936646</v>
+        <v>23.060053</v>
       </c>
       <c r="T106" t="n">
-        <v>20.088171</v>
+        <v>20.189786</v>
       </c>
       <c r="U106" t="n">
-        <v>17.310491</v>
+        <v>17.394307</v>
       </c>
       <c r="V106" t="n">
-        <v>14.821127</v>
+        <v>14.890192</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1.434251</v>
+        <v>1.48687</v>
       </c>
       <c r="F107" t="n">
-        <v>1.309154</v>
+        <v>1.367906</v>
       </c>
       <c r="G107" t="n">
-        <v>1.240254</v>
+        <v>1.297735</v>
       </c>
       <c r="H107" t="n">
-        <v>1.165311</v>
+        <v>1.219041</v>
       </c>
       <c r="I107" t="n">
-        <v>1.074061</v>
+        <v>1.122823</v>
       </c>
       <c r="J107" t="n">
-        <v>0.967865</v>
+        <v>1.011083</v>
       </c>
       <c r="K107" t="n">
-        <v>0.849042</v>
+        <v>0.886348</v>
       </c>
       <c r="L107" t="n">
-        <v>0.746067</v>
+        <v>0.778336</v>
       </c>
       <c r="M107" t="n">
-        <v>0.676747</v>
+        <v>0.70553</v>
       </c>
       <c r="N107" t="n">
-        <v>0.6372679999999999</v>
+        <v>0.663879</v>
       </c>
       <c r="O107" t="n">
-        <v>0.604311</v>
+        <v>0.629042</v>
       </c>
       <c r="P107" t="n">
-        <v>0.593709</v>
+        <v>0.617505</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.587288</v>
+        <v>0.610331</v>
       </c>
       <c r="R107" t="n">
-        <v>0.570041</v>
+        <v>0.591899</v>
       </c>
       <c r="S107" t="n">
-        <v>0.534602</v>
+        <v>0.554547</v>
       </c>
       <c r="T107" t="n">
-        <v>0.484132</v>
+        <v>0.501645</v>
       </c>
       <c r="U107" t="n">
-        <v>0.429433</v>
+        <v>0.444469</v>
       </c>
       <c r="V107" t="n">
-        <v>0.37707</v>
+        <v>0.389823</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>34.386015</v>
+        <v>34.987945</v>
       </c>
       <c r="F108" t="n">
-        <v>32.281263</v>
+        <v>32.881455</v>
       </c>
       <c r="G108" t="n">
-        <v>30.334088</v>
+        <v>30.862639</v>
       </c>
       <c r="H108" t="n">
-        <v>27.693844</v>
+        <v>28.143001</v>
       </c>
       <c r="I108" t="n">
-        <v>24.494258</v>
+        <v>24.865905</v>
       </c>
       <c r="J108" t="n">
-        <v>21.039957</v>
+        <v>21.343049</v>
       </c>
       <c r="K108" t="n">
-        <v>17.562145</v>
+        <v>17.805229</v>
       </c>
       <c r="L108" t="n">
-        <v>14.718975</v>
+        <v>14.91622</v>
       </c>
       <c r="M108" t="n">
-        <v>12.797268</v>
+        <v>12.963248</v>
       </c>
       <c r="N108" t="n">
-        <v>11.620112</v>
+        <v>11.765882</v>
       </c>
       <c r="O108" t="n">
-        <v>10.695403</v>
+        <v>10.825001</v>
       </c>
       <c r="P108" t="n">
-        <v>10.263819</v>
+        <v>10.384582</v>
       </c>
       <c r="Q108" t="n">
-        <v>9.966334</v>
+        <v>10.081462</v>
       </c>
       <c r="R108" t="n">
-        <v>9.544496000000001</v>
+        <v>9.653149000000001</v>
       </c>
       <c r="S108" t="n">
-        <v>8.858855</v>
+        <v>8.958323</v>
       </c>
       <c r="T108" t="n">
-        <v>7.968712</v>
+        <v>8.056604999999999</v>
       </c>
       <c r="U108" t="n">
-        <v>7.043156</v>
+        <v>7.118913</v>
       </c>
       <c r="V108" t="n">
-        <v>6.179329</v>
+        <v>6.243625</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>29.345548</v>
+        <v>28.722039</v>
       </c>
       <c r="F109" t="n">
-        <v>32.709722</v>
+        <v>32.124372</v>
       </c>
       <c r="G109" t="n">
-        <v>29.314665</v>
+        <v>28.877564</v>
       </c>
       <c r="H109" t="n">
-        <v>24.081944</v>
+        <v>23.801507</v>
       </c>
       <c r="I109" t="n">
-        <v>19.221773</v>
+        <v>19.065603</v>
       </c>
       <c r="J109" t="n">
-        <v>15.313984</v>
+        <v>15.237512</v>
       </c>
       <c r="K109" t="n">
-        <v>12.142522</v>
+        <v>12.111695</v>
       </c>
       <c r="L109" t="n">
-        <v>9.822895000000001</v>
+        <v>9.814954</v>
       </c>
       <c r="M109" t="n">
-        <v>8.31732</v>
+        <v>8.319744999999999</v>
       </c>
       <c r="N109" t="n">
-        <v>7.391464</v>
+        <v>7.398306</v>
       </c>
       <c r="O109" t="n">
-        <v>6.666803</v>
+        <v>6.675039</v>
       </c>
       <c r="P109" t="n">
-        <v>6.267286</v>
+        <v>6.27582</v>
       </c>
       <c r="Q109" t="n">
-        <v>5.95025</v>
+        <v>5.958769</v>
       </c>
       <c r="R109" t="n">
-        <v>5.564883</v>
+        <v>5.572418</v>
       </c>
       <c r="S109" t="n">
-        <v>5.055339</v>
+        <v>5.060669</v>
       </c>
       <c r="T109" t="n">
-        <v>4.449498</v>
+        <v>4.452808</v>
       </c>
       <c r="U109" t="n">
-        <v>3.845467</v>
+        <v>3.8475</v>
       </c>
       <c r="V109" t="n">
-        <v>3.297511</v>
+        <v>3.298681</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>13.309061</v>
+        <v>13.263897</v>
       </c>
       <c r="F110" t="n">
-        <v>13.969683</v>
+        <v>13.95147</v>
       </c>
       <c r="G110" t="n">
-        <v>13.354172</v>
+        <v>13.363624</v>
       </c>
       <c r="H110" t="n">
-        <v>12.205714</v>
+        <v>12.229225</v>
       </c>
       <c r="I110" t="n">
-        <v>10.855209</v>
+        <v>10.880073</v>
       </c>
       <c r="J110" t="n">
-        <v>9.463877</v>
+        <v>9.482972</v>
       </c>
       <c r="K110" t="n">
-        <v>8.085874</v>
+        <v>8.096355000000001</v>
       </c>
       <c r="L110" t="n">
-        <v>6.964798</v>
+        <v>6.967455</v>
       </c>
       <c r="M110" t="n">
-        <v>6.217733</v>
+        <v>6.2146</v>
       </c>
       <c r="N110" t="n">
-        <v>5.773325</v>
+        <v>5.76645</v>
       </c>
       <c r="O110" t="n">
-        <v>5.405356</v>
+        <v>5.396204</v>
       </c>
       <c r="P110" t="n">
-        <v>5.259382</v>
+        <v>5.248401</v>
       </c>
       <c r="Q110" t="n">
-        <v>5.175147</v>
+        <v>5.162389</v>
       </c>
       <c r="R110" t="n">
-        <v>5.015055</v>
+        <v>5.00062</v>
       </c>
       <c r="S110" t="n">
-        <v>4.694516</v>
+        <v>4.679106</v>
       </c>
       <c r="T110" t="n">
-        <v>4.247683</v>
+        <v>4.232159</v>
       </c>
       <c r="U110" t="n">
-        <v>3.771965</v>
+        <v>3.756818</v>
       </c>
       <c r="V110" t="n">
-        <v>3.32409</v>
+        <v>3.309457</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>91.79767</v>
+        <v>91.230919</v>
       </c>
       <c r="F111" t="n">
-        <v>95.56187</v>
+        <v>95.17035799999999</v>
       </c>
       <c r="G111" t="n">
-        <v>89.758996</v>
+        <v>89.525088</v>
       </c>
       <c r="H111" t="n">
-        <v>80.23296499999999</v>
+        <v>80.103461</v>
       </c>
       <c r="I111" t="n">
-        <v>69.61639599999999</v>
+        <v>69.550282</v>
       </c>
       <c r="J111" t="n">
-        <v>59.138417</v>
+        <v>59.103671</v>
       </c>
       <c r="K111" t="n">
-        <v>49.027437</v>
+        <v>49.006533</v>
       </c>
       <c r="L111" t="n">
-        <v>40.78692</v>
+        <v>40.772538</v>
       </c>
       <c r="M111" t="n">
-        <v>35.068452</v>
+        <v>35.05913</v>
       </c>
       <c r="N111" t="n">
-        <v>31.408947</v>
+        <v>31.401794</v>
       </c>
       <c r="O111" t="n">
-        <v>28.415476</v>
+        <v>28.40639</v>
       </c>
       <c r="P111" t="n">
-        <v>26.721461</v>
+        <v>26.705949</v>
       </c>
       <c r="Q111" t="n">
-        <v>25.424759</v>
+        <v>25.398336</v>
       </c>
       <c r="R111" t="n">
-        <v>23.818645</v>
+        <v>23.779806</v>
       </c>
       <c r="S111" t="n">
-        <v>21.571754</v>
+        <v>21.52286</v>
       </c>
       <c r="T111" t="n">
-        <v>18.938025</v>
+        <v>18.883555</v>
       </c>
       <c r="U111" t="n">
-        <v>16.356417</v>
+        <v>16.301334</v>
       </c>
       <c r="V111" t="n">
-        <v>14.032656</v>
+        <v>13.979644</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>111.90443</v>
+        <v>112.201325</v>
       </c>
       <c r="F112" t="n">
-        <v>113.363966</v>
+        <v>113.881991</v>
       </c>
       <c r="G112" t="n">
-        <v>106.591976</v>
+        <v>107.34953</v>
       </c>
       <c r="H112" t="n">
-        <v>96.156976</v>
+        <v>97.058886</v>
       </c>
       <c r="I112" t="n">
-        <v>84.450802</v>
+        <v>85.387381</v>
       </c>
       <c r="J112" t="n">
-        <v>72.625934</v>
+        <v>73.51111299999999</v>
       </c>
       <c r="K112" t="n">
-        <v>61.070295</v>
+        <v>61.850576</v>
       </c>
       <c r="L112" t="n">
-        <v>51.70451</v>
+        <v>52.377734</v>
       </c>
       <c r="M112" t="n">
-        <v>45.405925</v>
+        <v>45.999364</v>
       </c>
       <c r="N112" t="n">
-        <v>41.58898</v>
+        <v>42.132685</v>
       </c>
       <c r="O112" t="n">
-        <v>38.560943</v>
+        <v>39.063997</v>
       </c>
       <c r="P112" t="n">
-        <v>37.276817</v>
+        <v>37.760682</v>
       </c>
       <c r="Q112" t="n">
-        <v>36.47269</v>
+        <v>36.943955</v>
       </c>
       <c r="R112" t="n">
-        <v>35.188373</v>
+        <v>35.639413</v>
       </c>
       <c r="S112" t="n">
-        <v>32.934915</v>
+        <v>33.350733</v>
       </c>
       <c r="T112" t="n">
-        <v>29.858563</v>
+        <v>30.22879</v>
       </c>
       <c r="U112" t="n">
-        <v>26.597651</v>
+        <v>26.920201</v>
       </c>
       <c r="V112" t="n">
-        <v>23.528013</v>
+        <v>23.805815</v>
       </c>
     </row>
     <row r="113">
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15.598998</v>
+        <v>15.63891</v>
       </c>
       <c r="F113" t="n">
-        <v>16.294436</v>
+        <v>16.33335</v>
       </c>
       <c r="G113" t="n">
-        <v>12.716515</v>
+        <v>12.723311</v>
       </c>
       <c r="H113" t="n">
-        <v>10.163596</v>
+        <v>10.142544</v>
       </c>
       <c r="I113" t="n">
-        <v>8.387369</v>
+        <v>8.324311</v>
       </c>
       <c r="J113" t="n">
         <v>11.450557</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2.267628</v>
+        <v>2.235163</v>
       </c>
       <c r="F114" t="n">
-        <v>3.356494</v>
+        <v>3.324206</v>
       </c>
       <c r="G114" t="n">
-        <v>3.922833</v>
+        <v>3.905427</v>
       </c>
       <c r="H114" t="n">
-        <v>4.123148</v>
+        <v>4.114779</v>
       </c>
       <c r="I114" t="n">
-        <v>3.87699</v>
+        <v>3.874703</v>
       </c>
       <c r="J114" t="n">
         <v>3.366913</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>59.93093</v>
+        <v>59.923484</v>
       </c>
       <c r="F115" t="n">
-        <v>72.335291</v>
+        <v>72.328666</v>
       </c>
       <c r="G115" t="n">
-        <v>70.984143</v>
+        <v>70.994753</v>
       </c>
       <c r="H115" t="n">
-        <v>67.222724</v>
+        <v>67.252145</v>
       </c>
       <c r="I115" t="n">
-        <v>60.754108</v>
+        <v>60.819453</v>
       </c>
       <c r="J115" t="n">
         <v>52.022109</v>
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1.594998</v>
+        <v>1.572184</v>
       </c>
       <c r="F116" t="n">
-        <v>1.768922</v>
+        <v>1.731114</v>
       </c>
       <c r="G116" t="n">
-        <v>1.732406</v>
+        <v>1.690374</v>
       </c>
       <c r="H116" t="n">
-        <v>1.624217</v>
+        <v>1.582375</v>
       </c>
       <c r="I116" t="n">
-        <v>1.470212</v>
+        <v>1.430623</v>
       </c>
       <c r="J116" t="n">
-        <v>1.314249</v>
+        <v>1.277382</v>
       </c>
       <c r="K116" t="n">
-        <v>1.142056</v>
+        <v>1.108712</v>
       </c>
       <c r="L116" t="n">
-        <v>0.974843</v>
+        <v>0.946352</v>
       </c>
       <c r="M116" t="n">
-        <v>0.840044</v>
+        <v>0.815986</v>
       </c>
       <c r="N116" t="n">
-        <v>0.727109</v>
+        <v>0.706619</v>
       </c>
       <c r="O116" t="n">
-        <v>0.629423</v>
+        <v>0.611713</v>
       </c>
       <c r="P116" t="n">
-        <v>0.5569</v>
+        <v>0.541109</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.491957</v>
+        <v>0.477812</v>
       </c>
       <c r="R116" t="n">
-        <v>0.428771</v>
+        <v>0.416161</v>
       </c>
       <c r="S116" t="n">
-        <v>0.3651</v>
+        <v>0.353973</v>
       </c>
       <c r="T116" t="n">
-        <v>0.305274</v>
+        <v>0.295447</v>
       </c>
       <c r="U116" t="n">
-        <v>0.255034</v>
+        <v>0.246139</v>
       </c>
       <c r="V116" t="n">
-        <v>0.215644</v>
+        <v>0.20723</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6.461658</v>
+        <v>6.465415</v>
       </c>
       <c r="F117" t="n">
-        <v>8.270454000000001</v>
+        <v>8.285933</v>
       </c>
       <c r="G117" t="n">
-        <v>8.470235000000001</v>
+        <v>8.491455</v>
       </c>
       <c r="H117" t="n">
-        <v>8.026816999999999</v>
+        <v>8.049474</v>
       </c>
       <c r="I117" t="n">
-        <v>7.225795</v>
+        <v>7.247501</v>
       </c>
       <c r="J117" t="n">
-        <v>6.368225</v>
+        <v>6.388129</v>
       </c>
       <c r="K117" t="n">
-        <v>5.432014</v>
+        <v>5.449528</v>
       </c>
       <c r="L117" t="n">
-        <v>4.457718</v>
+        <v>4.471205</v>
       </c>
       <c r="M117" t="n">
-        <v>3.657573</v>
+        <v>3.667421</v>
       </c>
       <c r="N117" t="n">
-        <v>3.025928</v>
+        <v>3.033249</v>
       </c>
       <c r="O117" t="n">
-        <v>2.528072</v>
+        <v>2.533797</v>
       </c>
       <c r="P117" t="n">
-        <v>2.17105</v>
+        <v>2.175767</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.865751</v>
+        <v>1.86968</v>
       </c>
       <c r="R117" t="n">
-        <v>1.587702</v>
+        <v>1.59097</v>
       </c>
       <c r="S117" t="n">
-        <v>1.325546</v>
+        <v>1.32826</v>
       </c>
       <c r="T117" t="n">
-        <v>1.087405</v>
+        <v>1.089674</v>
       </c>
       <c r="U117" t="n">
-        <v>0.889925</v>
+        <v>0.891872</v>
       </c>
       <c r="V117" t="n">
-        <v>0.738465</v>
+        <v>0.740246</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5.583495</v>
+        <v>5.589058</v>
       </c>
       <c r="F118" t="n">
-        <v>5.663528</v>
+        <v>5.670928</v>
       </c>
       <c r="G118" t="n">
-        <v>5.124879</v>
+        <v>5.130816</v>
       </c>
       <c r="H118" t="n">
-        <v>4.524827</v>
+        <v>4.528852</v>
       </c>
       <c r="I118" t="n">
-        <v>3.918803</v>
+        <v>3.921218</v>
       </c>
       <c r="J118" t="n">
-        <v>3.380756</v>
+        <v>3.3819</v>
       </c>
       <c r="K118" t="n">
-        <v>2.848898</v>
+        <v>2.849044</v>
       </c>
       <c r="L118" t="n">
-        <v>2.325475</v>
+        <v>2.324247</v>
       </c>
       <c r="M118" t="n">
-        <v>1.910899</v>
+        <v>1.908592</v>
       </c>
       <c r="N118" t="n">
-        <v>1.593849</v>
+        <v>1.59103</v>
       </c>
       <c r="O118" t="n">
-        <v>1.348623</v>
+        <v>1.345724</v>
       </c>
       <c r="P118" t="n">
-        <v>1.176146</v>
+        <v>1.173283</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.028034</v>
+        <v>1.025261</v>
       </c>
       <c r="R118" t="n">
-        <v>0.889373</v>
+        <v>0.886752</v>
       </c>
       <c r="S118" t="n">
-        <v>0.754229</v>
+        <v>0.751798</v>
       </c>
       <c r="T118" t="n">
-        <v>0.62914</v>
+        <v>0.626891</v>
       </c>
       <c r="U118" t="n">
-        <v>0.524218</v>
+        <v>0.522108</v>
       </c>
       <c r="V118" t="n">
-        <v>0.441519</v>
+        <v>0.439472</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2.472709</v>
+        <v>2.471426</v>
       </c>
       <c r="F119" t="n">
-        <v>3.03281</v>
+        <v>3.033496</v>
       </c>
       <c r="G119" t="n">
-        <v>3.259239</v>
+        <v>3.262576</v>
       </c>
       <c r="H119" t="n">
-        <v>3.286713</v>
+        <v>3.291881</v>
       </c>
       <c r="I119" t="n">
-        <v>3.133068</v>
+        <v>3.139038</v>
       </c>
       <c r="J119" t="n">
-        <v>2.900739</v>
+        <v>2.906816</v>
       </c>
       <c r="K119" t="n">
-        <v>2.580446</v>
+        <v>2.58611</v>
       </c>
       <c r="L119" t="n">
-        <v>2.19687</v>
+        <v>2.201151</v>
       </c>
       <c r="M119" t="n">
-        <v>1.867954</v>
+        <v>1.870866</v>
       </c>
       <c r="N119" t="n">
-        <v>1.602535</v>
+        <v>1.604529</v>
       </c>
       <c r="O119" t="n">
-        <v>1.386474</v>
+        <v>1.387964</v>
       </c>
       <c r="P119" t="n">
-        <v>1.228885</v>
+        <v>1.23008</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.085674</v>
+        <v>1.086635</v>
       </c>
       <c r="R119" t="n">
-        <v>0.946538</v>
+        <v>0.947296</v>
       </c>
       <c r="S119" t="n">
-        <v>0.808535</v>
+        <v>0.809117</v>
       </c>
       <c r="T119" t="n">
-        <v>0.678375</v>
+        <v>0.678825</v>
       </c>
       <c r="U119" t="n">
-        <v>0.56689</v>
+        <v>0.567254</v>
       </c>
       <c r="V119" t="n">
-        <v>0.47786</v>
+        <v>0.478163</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
+        <v>0.005403</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.009082</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.010236</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.010334</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.009377999999999999</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.008612</v>
+      </c>
+      <c r="L120" t="n">
         <v>0.00746</v>
       </c>
-      <c r="F120" t="n">
-        <v>0.01252</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0.014102</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.014232</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.013659</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0.01291</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0.011852</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0.010268</v>
-      </c>
       <c r="M120" t="n">
-        <v>0.008789999999999999</v>
+        <v>0.006385</v>
       </c>
       <c r="N120" t="n">
-        <v>0.007593</v>
+        <v>0.005515</v>
       </c>
       <c r="O120" t="n">
-        <v>0.006648</v>
+        <v>0.004828</v>
       </c>
       <c r="P120" t="n">
-        <v>0.005997</v>
+        <v>0.004355</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.005429</v>
+        <v>0.003943</v>
       </c>
       <c r="R120" t="n">
-        <v>0.004896</v>
+        <v>0.003556</v>
       </c>
       <c r="S120" t="n">
-        <v>0.004372</v>
+        <v>0.003177</v>
       </c>
       <c r="T120" t="n">
-        <v>0.003912</v>
+        <v>0.002843</v>
       </c>
       <c r="U120" t="n">
-        <v>0.003589</v>
+        <v>0.00261</v>
       </c>
       <c r="V120" t="n">
-        <v>0.003442</v>
+        <v>0.002505</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.119871</v>
+        <v>0.086826</v>
       </c>
       <c r="F121" t="n">
-        <v>0.174743</v>
+        <v>0.126755</v>
       </c>
       <c r="G121" t="n">
-        <v>0.176651</v>
+        <v>0.128223</v>
       </c>
       <c r="H121" t="n">
-        <v>0.167126</v>
+        <v>0.121351</v>
       </c>
       <c r="I121" t="n">
-        <v>0.155903</v>
+        <v>0.113229</v>
       </c>
       <c r="J121" t="n">
-        <v>0.146818</v>
+        <v>0.106654</v>
       </c>
       <c r="K121" t="n">
-        <v>0.136119</v>
+        <v>0.098902</v>
       </c>
       <c r="L121" t="n">
-        <v>0.12223</v>
+        <v>0.088805</v>
       </c>
       <c r="M121" t="n">
-        <v>0.109238</v>
+        <v>0.079349</v>
       </c>
       <c r="N121" t="n">
-        <v>0.09751600000000001</v>
+        <v>0.070824</v>
       </c>
       <c r="O121" t="n">
-        <v>0.08683299999999999</v>
+        <v>0.06306200000000001</v>
       </c>
       <c r="P121" t="n">
-        <v>0.078946</v>
+        <v>0.057336</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.071786</v>
+        <v>0.052139</v>
       </c>
       <c r="R121" t="n">
-        <v>0.064999</v>
+        <v>0.047215</v>
       </c>
       <c r="S121" t="n">
-        <v>0.058547</v>
+        <v>0.042537</v>
       </c>
       <c r="T121" t="n">
-        <v>0.052776</v>
+        <v>0.038358</v>
       </c>
       <c r="U121" t="n">
-        <v>0.048568</v>
+        <v>0.035319</v>
       </c>
       <c r="V121" t="n">
-        <v>0.046881</v>
+        <v>0.034123</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>114.182286</v>
+        <v>114.232165</v>
       </c>
       <c r="F122" t="n">
-        <v>124.706538</v>
+        <v>124.772207</v>
       </c>
       <c r="G122" t="n">
-        <v>122.907564</v>
+        <v>122.971397</v>
       </c>
       <c r="H122" t="n">
-        <v>117.129461</v>
+        <v>117.189125</v>
       </c>
       <c r="I122" t="n">
-        <v>108.320106</v>
+        <v>108.376016</v>
       </c>
       <c r="J122" t="n">
-        <v>99.040449</v>
+        <v>99.093886</v>
       </c>
       <c r="K122" t="n">
-        <v>87.91236600000001</v>
+        <v>87.96284300000001</v>
       </c>
       <c r="L122" t="n">
-        <v>77.318624</v>
+        <v>77.36680800000001</v>
       </c>
       <c r="M122" t="n">
-        <v>68.772099</v>
+        <v>68.817998</v>
       </c>
       <c r="N122" t="n">
-        <v>61.116907</v>
+        <v>61.159672</v>
       </c>
       <c r="O122" t="n">
-        <v>54.02216</v>
+        <v>54.061145</v>
       </c>
       <c r="P122" t="n">
-        <v>48.668115</v>
+        <v>48.704109</v>
       </c>
       <c r="Q122" t="n">
-        <v>43.744057</v>
+        <v>43.777219</v>
       </c>
       <c r="R122" t="n">
-        <v>38.882177</v>
+        <v>38.912504</v>
       </c>
       <c r="S122" t="n">
-        <v>33.928525</v>
+        <v>33.955993</v>
       </c>
       <c r="T122" t="n">
-        <v>29.159786</v>
+        <v>29.184631</v>
       </c>
       <c r="U122" t="n">
-        <v>25.025945</v>
+        <v>25.048867</v>
       </c>
       <c r="V122" t="n">
-        <v>21.661477</v>
+        <v>21.683549</v>
       </c>
     </row>
     <row r="123">
@@ -9725,10 +9725,10 @@
         <v>0.822208</v>
       </c>
       <c r="F123" t="n">
-        <v>0.775967</v>
+        <v>0.775968</v>
       </c>
       <c r="G123" t="n">
-        <v>0.660822</v>
+        <v>0.660823</v>
       </c>
       <c r="H123" t="n">
         <v>0.552423</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5.380588</v>
+        <v>5.380615</v>
       </c>
       <c r="F124" t="n">
-        <v>4.956897</v>
+        <v>4.956912</v>
       </c>
       <c r="G124" t="n">
-        <v>4.376236</v>
+        <v>4.376247</v>
       </c>
       <c r="H124" t="n">
-        <v>3.868147</v>
+        <v>3.868154</v>
       </c>
       <c r="I124" t="n">
-        <v>3.280651</v>
+        <v>3.280654</v>
       </c>
       <c r="J124" t="n">
         <v>2.624965</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>16.804918</v>
+        <v>16.804891</v>
       </c>
       <c r="F125" t="n">
-        <v>17.499261</v>
+        <v>17.499246</v>
       </c>
       <c r="G125" t="n">
-        <v>17.932231</v>
+        <v>17.93222</v>
       </c>
       <c r="H125" t="n">
-        <v>17.376031</v>
+        <v>17.376024</v>
       </c>
       <c r="I125" t="n">
-        <v>15.32031</v>
+        <v>15.320307</v>
       </c>
       <c r="J125" t="n">
         <v>12.257256</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3.326576</v>
+        <v>5.28933</v>
       </c>
       <c r="F130" t="n">
-        <v>3.441919</v>
+        <v>5.218745</v>
       </c>
       <c r="G130" t="n">
-        <v>3.737662</v>
+        <v>5.475788</v>
       </c>
       <c r="H130" t="n">
-        <v>3.421956</v>
+        <v>4.84728</v>
       </c>
       <c r="I130" t="n">
-        <v>2.631739</v>
+        <v>3.465384</v>
       </c>
       <c r="J130" t="n">
         <v>1.513432</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.773793</v>
+        <v>1.083461</v>
       </c>
       <c r="F131" t="n">
-        <v>0.910813</v>
+        <v>1.218876</v>
       </c>
       <c r="G131" t="n">
-        <v>1.100594</v>
+        <v>1.39496</v>
       </c>
       <c r="H131" t="n">
-        <v>1.150307</v>
+        <v>1.381443</v>
       </c>
       <c r="I131" t="n">
-        <v>1.089869</v>
+        <v>1.220781</v>
       </c>
       <c r="J131" t="n">
         <v>0.938266</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>80.00581200000001</v>
+        <v>83.506348</v>
       </c>
       <c r="F132" t="n">
-        <v>117.880668</v>
+        <v>119.663014</v>
       </c>
       <c r="G132" t="n">
-        <v>161.09325</v>
+        <v>161.341762</v>
       </c>
       <c r="H132" t="n">
-        <v>183.627687</v>
+        <v>183.072963</v>
       </c>
       <c r="I132" t="n">
-        <v>185.530276</v>
+        <v>185.032488</v>
       </c>
       <c r="J132" t="n">
         <v>170.829725</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>98.705365</v>
+        <v>96.593878</v>
       </c>
       <c r="F133" t="n">
-        <v>86.720585</v>
+        <v>85.939548</v>
       </c>
       <c r="G133" t="n">
-        <v>75.012337</v>
+        <v>75.197261</v>
       </c>
       <c r="H133" t="n">
-        <v>66.566219</v>
+        <v>67.164968</v>
       </c>
       <c r="I133" t="n">
-        <v>63.825672</v>
+        <v>64.233316</v>
       </c>
       <c r="J133" t="n">
         <v>63.056937</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3.040584</v>
+        <v>3.618281</v>
       </c>
       <c r="F134" t="n">
-        <v>5.213154</v>
+        <v>5.582281</v>
       </c>
       <c r="G134" t="n">
-        <v>8.673185</v>
+        <v>8.877331999999999</v>
       </c>
       <c r="H134" t="n">
-        <v>11.578508</v>
+        <v>11.6524</v>
       </c>
       <c r="I134" t="n">
-        <v>13.424309</v>
+        <v>13.433166</v>
       </c>
       <c r="J134" t="n">
         <v>14.295602</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>24.377191</v>
+        <v>23.770872</v>
       </c>
       <c r="F135" t="n">
-        <v>30.185373</v>
+        <v>29.581112</v>
       </c>
       <c r="G135" t="n">
-        <v>32.707406</v>
+        <v>32.147999</v>
       </c>
       <c r="H135" t="n">
-        <v>31.692685</v>
+        <v>31.303768</v>
       </c>
       <c r="I135" t="n">
-        <v>30.024227</v>
+        <v>29.826463</v>
       </c>
       <c r="J135" t="n">
         <v>28.249175</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1.519135</v>
+        <v>2.418779</v>
       </c>
       <c r="F136" t="n">
-        <v>1.547458</v>
+        <v>2.232416</v>
       </c>
       <c r="G136" t="n">
-        <v>1.977658</v>
+        <v>2.487098</v>
       </c>
       <c r="H136" t="n">
-        <v>2.560839</v>
+        <v>2.872155</v>
       </c>
       <c r="I136" t="n">
-        <v>3.050503</v>
+        <v>3.196059</v>
       </c>
       <c r="J136" t="n">
         <v>3.231714</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2.874312</v>
+        <v>3.04331</v>
       </c>
       <c r="F137" t="n">
-        <v>3.874733</v>
+        <v>3.990918</v>
       </c>
       <c r="G137" t="n">
-        <v>5.22254</v>
+        <v>5.280882</v>
       </c>
       <c r="H137" t="n">
-        <v>5.933006</v>
+        <v>5.950622</v>
       </c>
       <c r="I137" t="n">
-        <v>6.027695</v>
+        <v>6.029078</v>
       </c>
       <c r="J137" t="n">
         <v>5.681172</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1.984153</v>
+        <v>2.712608</v>
       </c>
       <c r="F138" t="n">
-        <v>2.45729</v>
+        <v>3.037521</v>
       </c>
       <c r="G138" t="n">
-        <v>3.201605</v>
+        <v>3.680899</v>
       </c>
       <c r="H138" t="n">
-        <v>3.717586</v>
+        <v>4.041622</v>
       </c>
       <c r="I138" t="n">
-        <v>4.069886</v>
+        <v>4.22554</v>
       </c>
       <c r="J138" t="n">
         <v>4.258705</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3.716238</v>
+        <v>4.733305</v>
       </c>
       <c r="F139" t="n">
-        <v>4.845024</v>
+        <v>5.720732</v>
       </c>
       <c r="G139" t="n">
-        <v>5.956166</v>
+        <v>6.782926</v>
       </c>
       <c r="H139" t="n">
-        <v>6.120353</v>
+        <v>6.790274</v>
       </c>
       <c r="I139" t="n">
-        <v>5.735804</v>
+        <v>6.125932</v>
       </c>
       <c r="J139" t="n">
         <v>5.039542</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>18.327216</v>
+        <v>23.834693</v>
       </c>
       <c r="F140" t="n">
-        <v>27.751415</v>
+        <v>31.630449</v>
       </c>
       <c r="G140" t="n">
-        <v>43.008712</v>
+        <v>45.780047</v>
       </c>
       <c r="H140" t="n">
-        <v>54.14526</v>
+        <v>55.86343</v>
       </c>
       <c r="I140" t="n">
-        <v>59.085724</v>
+        <v>59.922614</v>
       </c>
       <c r="J140" t="n">
         <v>58.726161</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>108.007897</v>
+        <v>104.435695</v>
       </c>
       <c r="F141" t="n">
-        <v>143.845774</v>
+        <v>139.930484</v>
       </c>
       <c r="G141" t="n">
-        <v>169.493341</v>
+        <v>165.297338</v>
       </c>
       <c r="H141" t="n">
-        <v>171.511166</v>
+        <v>168.193365</v>
       </c>
       <c r="I141" t="n">
-        <v>161.693103</v>
+        <v>159.893462</v>
       </c>
       <c r="J141" t="n">
         <v>145.448753</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>240.425539</v>
+        <v>232.04325</v>
       </c>
       <c r="F142" t="n">
-        <v>182.419989</v>
+        <v>177.348097</v>
       </c>
       <c r="G142" t="n">
-        <v>109.480338</v>
+        <v>106.920502</v>
       </c>
       <c r="H142" t="n">
-        <v>70.54343299999999</v>
+        <v>69.43471599999999</v>
       </c>
       <c r="I142" t="n">
-        <v>54.422842</v>
+        <v>54.007363</v>
       </c>
       <c r="J142" t="n">
         <v>49.364725</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2.13748</v>
+        <v>1.758883</v>
       </c>
       <c r="F146" t="n">
-        <v>3.298026</v>
+        <v>2.731507</v>
       </c>
       <c r="G146" t="n">
-        <v>3.933329</v>
+        <v>3.260018</v>
       </c>
       <c r="H146" t="n">
-        <v>3.967348</v>
+        <v>3.36201</v>
       </c>
       <c r="I146" t="n">
-        <v>3.702331</v>
+        <v>3.318595</v>
       </c>
       <c r="J146" t="n">
         <v>3.486431</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.639023</v>
+        <v>0.662781</v>
       </c>
       <c r="F147" t="n">
-        <v>0.763226</v>
+        <v>0.784203</v>
       </c>
       <c r="G147" t="n">
-        <v>0.80244</v>
+        <v>0.808594</v>
       </c>
       <c r="H147" t="n">
-        <v>0.775938</v>
+        <v>0.770607</v>
       </c>
       <c r="I147" t="n">
-        <v>0.706322</v>
+        <v>0.7016019999999999</v>
       </c>
       <c r="J147" t="n">
         <v>0.628196</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>46.162959</v>
+        <v>46.517799</v>
       </c>
       <c r="F148" t="n">
-        <v>56.64581</v>
+        <v>57.191351</v>
       </c>
       <c r="G148" t="n">
-        <v>58.993196</v>
+        <v>59.660353</v>
       </c>
       <c r="H148" t="n">
-        <v>56.037059</v>
+        <v>56.647729</v>
       </c>
       <c r="I148" t="n">
-        <v>50.854687</v>
+        <v>51.243143</v>
       </c>
       <c r="J148" t="n">
         <v>45.253858</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6.293357</v>
+        <v>6.129503</v>
       </c>
       <c r="F149" t="n">
-        <v>7.378942</v>
+        <v>7.048616</v>
       </c>
       <c r="G149" t="n">
-        <v>8.116697</v>
+        <v>7.637026</v>
       </c>
       <c r="H149" t="n">
-        <v>8.613763000000001</v>
+        <v>8.018769000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>8.789764</v>
+        <v>8.132680000000001</v>
       </c>
       <c r="J149" t="n">
         <v>11.050091</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>23.272889</v>
+        <v>23.611135</v>
       </c>
       <c r="F150" t="n">
-        <v>23.840753</v>
+        <v>24.423135</v>
       </c>
       <c r="G150" t="n">
-        <v>23.179684</v>
+        <v>23.956073</v>
       </c>
       <c r="H150" t="n">
-        <v>21.159205</v>
+        <v>22.11429</v>
       </c>
       <c r="I150" t="n">
-        <v>16.703027</v>
+        <v>17.832265</v>
       </c>
       <c r="J150" t="n">
         <v>6.587164</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>12.177558</v>
+        <v>12.188239</v>
       </c>
       <c r="F151" t="n">
-        <v>13.833664</v>
+        <v>13.873996</v>
       </c>
       <c r="G151" t="n">
-        <v>14.652176</v>
+        <v>14.748289</v>
       </c>
       <c r="H151" t="n">
-        <v>14.403642</v>
+        <v>14.555036</v>
       </c>
       <c r="I151" t="n">
-        <v>12.616179</v>
+        <v>12.804137</v>
       </c>
       <c r="J151" t="n">
         <v>9.322357999999999</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15.996298</v>
+        <v>15.95489</v>
       </c>
       <c r="F152" t="n">
-        <v>18.309615</v>
+        <v>18.296996</v>
       </c>
       <c r="G152" t="n">
-        <v>18.71629</v>
+        <v>18.707909</v>
       </c>
       <c r="H152" t="n">
-        <v>17.835205</v>
+        <v>17.790263</v>
       </c>
       <c r="I152" t="n">
-        <v>15.636335</v>
+        <v>15.517106</v>
       </c>
       <c r="J152" t="n">
         <v>14.110713</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2.427269</v>
+        <v>2.270954</v>
       </c>
       <c r="F153" t="n">
-        <v>3.161576</v>
+        <v>2.852327</v>
       </c>
       <c r="G153" t="n">
-        <v>3.769032</v>
+        <v>3.343109</v>
       </c>
       <c r="H153" t="n">
-        <v>4.26325</v>
+        <v>3.750101</v>
       </c>
       <c r="I153" t="n">
-        <v>4.736392</v>
+        <v>4.149944</v>
       </c>
       <c r="J153" t="n">
         <v>7.565788</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1.946781</v>
+        <v>1.959432</v>
       </c>
       <c r="F154" t="n">
-        <v>2.143518</v>
+        <v>2.172997</v>
       </c>
       <c r="G154" t="n">
-        <v>2.112078</v>
+        <v>2.153549</v>
       </c>
       <c r="H154" t="n">
-        <v>1.909369</v>
+        <v>1.955976</v>
       </c>
       <c r="I154" t="n">
-        <v>1.532042</v>
+        <v>1.577608</v>
       </c>
       <c r="J154" t="n">
         <v>1.007004</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2.461043</v>
+        <v>2.461031</v>
       </c>
       <c r="F155" t="n">
-        <v>3.194074</v>
+        <v>3.194046</v>
       </c>
       <c r="G155" t="n">
-        <v>3.479574</v>
+        <v>3.479534</v>
       </c>
       <c r="H155" t="n">
-        <v>3.808944</v>
+        <v>3.808894</v>
       </c>
       <c r="I155" t="n">
-        <v>4.026635</v>
+        <v>4.026579</v>
       </c>
       <c r="J155" t="n">
-        <v>4.231604</v>
+        <v>4.231546</v>
       </c>
       <c r="K155" t="n">
-        <v>4.465184</v>
+        <v>4.465125</v>
       </c>
       <c r="L155" t="n">
-        <v>4.702019</v>
+        <v>4.70196</v>
       </c>
       <c r="M155" t="n">
-        <v>5.018336</v>
+        <v>5.018277</v>
       </c>
       <c r="N155" t="n">
-        <v>5.195442</v>
+        <v>5.195386</v>
       </c>
       <c r="O155" t="n">
-        <v>5.151018</v>
+        <v>5.150967</v>
       </c>
       <c r="P155" t="n">
-        <v>4.963998</v>
+        <v>4.963952</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.79293</v>
+        <v>4.792888</v>
       </c>
       <c r="R155" t="n">
-        <v>4.629221</v>
+        <v>4.629181</v>
       </c>
       <c r="S155" t="n">
-        <v>4.388944</v>
+        <v>4.388907</v>
       </c>
       <c r="T155" t="n">
-        <v>4.036844</v>
+        <v>4.036809</v>
       </c>
       <c r="U155" t="n">
-        <v>3.628583</v>
+        <v>3.628551</v>
       </c>
       <c r="V155" t="n">
-        <v>3.241488</v>
+        <v>3.241459</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>25.189261</v>
+        <v>25.18927</v>
       </c>
       <c r="F156" t="n">
-        <v>31.645968</v>
+        <v>31.645993</v>
       </c>
       <c r="G156" t="n">
-        <v>33.266264</v>
+        <v>33.266307</v>
       </c>
       <c r="H156" t="n">
-        <v>34.869531</v>
+        <v>34.86959</v>
       </c>
       <c r="I156" t="n">
-        <v>34.951116</v>
+        <v>34.951184</v>
       </c>
       <c r="J156" t="n">
-        <v>34.695686</v>
+        <v>34.695756</v>
       </c>
       <c r="K156" t="n">
-        <v>34.52161</v>
+        <v>34.521679</v>
       </c>
       <c r="L156" t="n">
-        <v>34.340409</v>
+        <v>34.340475</v>
       </c>
       <c r="M156" t="n">
-        <v>34.729288</v>
+        <v>34.729352</v>
       </c>
       <c r="N156" t="n">
-        <v>34.468157</v>
+        <v>34.468219</v>
       </c>
       <c r="O156" t="n">
-        <v>32.98748</v>
+        <v>32.987538</v>
       </c>
       <c r="P156" t="n">
-        <v>30.752298</v>
+        <v>30.752353</v>
       </c>
       <c r="Q156" t="n">
-        <v>28.665619</v>
+        <v>28.66567</v>
       </c>
       <c r="R156" t="n">
-        <v>26.6603</v>
+        <v>26.660349</v>
       </c>
       <c r="S156" t="n">
-        <v>24.302692</v>
+        <v>24.302738</v>
       </c>
       <c r="T156" t="n">
-        <v>21.482418</v>
+        <v>21.48246</v>
       </c>
       <c r="U156" t="n">
-        <v>18.575031</v>
+        <v>18.575069</v>
       </c>
       <c r="V156" t="n">
-        <v>15.981372</v>
+        <v>15.981406</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.384682</v>
+        <v>0.384683</v>
       </c>
       <c r="F157" t="n">
-        <v>0.594662</v>
+        <v>0.594665</v>
       </c>
       <c r="G157" t="n">
-        <v>0.7040419999999999</v>
+        <v>0.704047</v>
       </c>
       <c r="H157" t="n">
-        <v>0.760182</v>
+        <v>0.760189</v>
       </c>
       <c r="I157" t="n">
-        <v>0.747042</v>
+        <v>0.747049</v>
       </c>
       <c r="J157" t="n">
-        <v>0.718279</v>
+        <v>0.718285</v>
       </c>
       <c r="K157" t="n">
-        <v>0.696334</v>
+        <v>0.69634</v>
       </c>
       <c r="L157" t="n">
-        <v>0.678681</v>
+        <v>0.678687</v>
       </c>
       <c r="M157" t="n">
-        <v>0.674019</v>
+        <v>0.674024</v>
       </c>
       <c r="N157" t="n">
-        <v>0.641967</v>
+        <v>0.641972</v>
       </c>
       <c r="O157" t="n">
-        <v>0.582139</v>
+        <v>0.582142</v>
       </c>
       <c r="P157" t="n">
-        <v>0.517115</v>
+        <v>0.517118</v>
       </c>
       <c r="Q157" t="n">
-        <v>0.468363</v>
+        <v>0.468366</v>
       </c>
       <c r="R157" t="n">
-        <v>0.431296</v>
+        <v>0.431299</v>
       </c>
       <c r="S157" t="n">
-        <v>0.394213</v>
+        <v>0.394216</v>
       </c>
       <c r="T157" t="n">
-        <v>0.351638</v>
+        <v>0.351639</v>
       </c>
       <c r="U157" t="n">
-        <v>0.30744</v>
+        <v>0.307442</v>
       </c>
       <c r="V157" t="n">
-        <v>0.267356</v>
+        <v>0.267358</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5.810945</v>
+        <v>5.810956</v>
       </c>
       <c r="F158" t="n">
-        <v>6.24603</v>
+        <v>6.246049</v>
       </c>
       <c r="G158" t="n">
-        <v>5.613004</v>
+        <v>5.613023</v>
       </c>
       <c r="H158" t="n">
-        <v>5.236688</v>
+        <v>5.236705</v>
       </c>
       <c r="I158" t="n">
-        <v>4.895471</v>
+        <v>4.895487</v>
       </c>
       <c r="J158" t="n">
-        <v>4.677707</v>
+        <v>4.677722</v>
       </c>
       <c r="K158" t="n">
-        <v>4.591604</v>
+        <v>4.591618</v>
       </c>
       <c r="L158" t="n">
-        <v>4.532774</v>
+        <v>4.532788</v>
       </c>
       <c r="M158" t="n">
-        <v>4.546566</v>
+        <v>4.546579</v>
       </c>
       <c r="N158" t="n">
-        <v>4.355143</v>
+        <v>4.355154</v>
       </c>
       <c r="O158" t="n">
-        <v>3.954162</v>
+        <v>3.954171</v>
       </c>
       <c r="P158" t="n">
-        <v>3.483391</v>
+        <v>3.483397</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.100393</v>
+        <v>3.100398</v>
       </c>
       <c r="R158" t="n">
-        <v>2.790412</v>
+        <v>2.790416</v>
       </c>
       <c r="S158" t="n">
-        <v>2.489954</v>
+        <v>2.489956</v>
       </c>
       <c r="T158" t="n">
-        <v>2.168221</v>
+        <v>2.168224</v>
       </c>
       <c r="U158" t="n">
-        <v>1.850003</v>
+        <v>1.850005</v>
       </c>
       <c r="V158" t="n">
-        <v>1.573209</v>
+        <v>1.573211</v>
       </c>
     </row>
     <row r="159">
@@ -12458,55 +12458,55 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.468289</v>
+        <v>0.468291</v>
       </c>
       <c r="F159" t="n">
-        <v>0.55205</v>
+        <v>0.552053</v>
       </c>
       <c r="G159" t="n">
-        <v>0.550433</v>
+        <v>0.550437</v>
       </c>
       <c r="H159" t="n">
-        <v>0.547489</v>
+        <v>0.547494</v>
       </c>
       <c r="I159" t="n">
-        <v>0.523076</v>
+        <v>0.523082</v>
       </c>
       <c r="J159" t="n">
-        <v>0.493669</v>
+        <v>0.493674</v>
       </c>
       <c r="K159" t="n">
-        <v>0.474607</v>
+        <v>0.474612</v>
       </c>
       <c r="L159" t="n">
-        <v>0.45781</v>
+        <v>0.457814</v>
       </c>
       <c r="M159" t="n">
-        <v>0.459082</v>
+        <v>0.459086</v>
       </c>
       <c r="N159" t="n">
-        <v>0.446375</v>
+        <v>0.446379</v>
       </c>
       <c r="O159" t="n">
-        <v>0.413629</v>
+        <v>0.413632</v>
       </c>
       <c r="P159" t="n">
-        <v>0.368897</v>
+        <v>0.368899</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.328169</v>
+        <v>0.328171</v>
       </c>
       <c r="R159" t="n">
-        <v>0.290553</v>
+        <v>0.290554</v>
       </c>
       <c r="S159" t="n">
-        <v>0.250871</v>
+        <v>0.250873</v>
       </c>
       <c r="T159" t="n">
-        <v>0.20828</v>
+        <v>0.208282</v>
       </c>
       <c r="U159" t="n">
-        <v>0.168616</v>
+        <v>0.168617</v>
       </c>
       <c r="V159" t="n">
         <v>0.137061</v>
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2.15881</v>
+        <v>2.1588</v>
       </c>
       <c r="F160" t="n">
-        <v>2.706573</v>
+        <v>2.70655</v>
       </c>
       <c r="G160" t="n">
-        <v>2.878966</v>
+        <v>2.878934</v>
       </c>
       <c r="H160" t="n">
-        <v>3.124161</v>
+        <v>3.124123</v>
       </c>
       <c r="I160" t="n">
-        <v>3.335824</v>
+        <v>3.335786</v>
       </c>
       <c r="J160" t="n">
-        <v>3.566824</v>
+        <v>3.566787</v>
       </c>
       <c r="K160" t="n">
-        <v>3.847857</v>
+        <v>3.847823</v>
       </c>
       <c r="L160" t="n">
-        <v>4.13612</v>
+        <v>4.13609</v>
       </c>
       <c r="M160" t="n">
-        <v>4.470468</v>
+        <v>4.470441</v>
       </c>
       <c r="N160" t="n">
-        <v>4.581916</v>
+        <v>4.581891</v>
       </c>
       <c r="O160" t="n">
-        <v>4.429821</v>
+        <v>4.429799</v>
       </c>
       <c r="P160" t="n">
-        <v>4.14489</v>
+        <v>4.14487</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.902928</v>
+        <v>3.902911</v>
       </c>
       <c r="R160" t="n">
-        <v>3.691678</v>
+        <v>3.691662</v>
       </c>
       <c r="S160" t="n">
-        <v>3.434113</v>
+        <v>3.434099</v>
       </c>
       <c r="T160" t="n">
-        <v>3.095845</v>
+        <v>3.095832</v>
       </c>
       <c r="U160" t="n">
-        <v>2.721354</v>
+        <v>2.721343</v>
       </c>
       <c r="V160" t="n">
-        <v>2.369455</v>
+        <v>2.369445</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2.33649</v>
+        <v>2.369335</v>
       </c>
       <c r="F162" t="n">
-        <v>1.677541</v>
+        <v>1.714589</v>
       </c>
       <c r="G162" t="n">
-        <v>1.131869</v>
+        <v>1.162711</v>
       </c>
       <c r="H162" t="n">
-        <v>0.8233</v>
+        <v>0.850661</v>
       </c>
       <c r="I162" t="n">
-        <v>0.614845</v>
+        <v>0.6452909999999999</v>
       </c>
       <c r="J162" t="n">
         <v>0.199497</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.532888</v>
+        <v>0.532532</v>
       </c>
       <c r="F163" t="n">
-        <v>0.637219</v>
+        <v>0.637907</v>
       </c>
       <c r="G163" t="n">
-        <v>0.702323</v>
+        <v>0.706678</v>
       </c>
       <c r="H163" t="n">
-        <v>0.711301</v>
+        <v>0.719573</v>
       </c>
       <c r="I163" t="n">
-        <v>0.64838</v>
+        <v>0.662183</v>
       </c>
       <c r="J163" t="n">
         <v>0.404066</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3.326559</v>
+        <v>3.129004</v>
       </c>
       <c r="F164" t="n">
-        <v>4.600563</v>
+        <v>4.302031</v>
       </c>
       <c r="G164" t="n">
-        <v>5.454974</v>
+        <v>5.143621</v>
       </c>
       <c r="H164" t="n">
-        <v>6.028578</v>
+        <v>5.701166</v>
       </c>
       <c r="I164" t="n">
-        <v>6.37063</v>
+        <v>5.970223</v>
       </c>
       <c r="J164" t="n">
         <v>10.124819</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3.031839</v>
+        <v>2.996456</v>
       </c>
       <c r="F165" t="n">
-        <v>3.688477</v>
+        <v>3.624292</v>
       </c>
       <c r="G165" t="n">
-        <v>3.70858</v>
+        <v>3.598972</v>
       </c>
       <c r="H165" t="n">
-        <v>3.669085</v>
+        <v>3.497494</v>
       </c>
       <c r="I165" t="n">
-        <v>3.713818</v>
+        <v>3.433763</v>
       </c>
       <c r="J165" t="n">
         <v>6.987681</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>9.457107000000001</v>
+        <v>8.341772000000001</v>
       </c>
       <c r="F166" t="n">
-        <v>12.758249</v>
+        <v>10.693548</v>
       </c>
       <c r="G166" t="n">
-        <v>14.672493</v>
+        <v>11.911222</v>
       </c>
       <c r="H166" t="n">
-        <v>16.817135</v>
+        <v>13.215477</v>
       </c>
       <c r="I166" t="n">
-        <v>21.679757</v>
+        <v>16.375914</v>
       </c>
       <c r="J166" t="n">
         <v>84.456521</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>80.49750400000001</v>
+        <v>81.527824</v>
       </c>
       <c r="F167" t="n">
-        <v>83.035166</v>
+        <v>84.693183</v>
       </c>
       <c r="G167" t="n">
-        <v>78.573649</v>
+        <v>80.570289</v>
       </c>
       <c r="H167" t="n">
-        <v>73.380931</v>
+        <v>75.84519299999999</v>
       </c>
       <c r="I167" t="n">
-        <v>63.723584</v>
+        <v>67.291067</v>
       </c>
       <c r="J167" t="n">
         <v>13.755676</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1.431479</v>
+        <v>1.450052</v>
       </c>
       <c r="F168" t="n">
-        <v>1.637822</v>
+        <v>1.671976</v>
       </c>
       <c r="G168" t="n">
-        <v>1.681327</v>
+        <v>1.727412</v>
       </c>
       <c r="H168" t="n">
-        <v>1.644237</v>
+        <v>1.705374</v>
       </c>
       <c r="I168" t="n">
-        <v>1.451264</v>
+        <v>1.543312</v>
       </c>
       <c r="J168" t="n">
         <v>0.170079</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>39.287667</v>
+        <v>38.516616</v>
       </c>
       <c r="F169" t="n">
-        <v>47.571558</v>
+        <v>45.98791</v>
       </c>
       <c r="G169" t="n">
-        <v>51.348599</v>
+        <v>49.040449</v>
       </c>
       <c r="H169" t="n">
-        <v>55.041166</v>
+        <v>51.996024</v>
       </c>
       <c r="I169" t="n">
-        <v>59.082435</v>
+        <v>54.767886</v>
       </c>
       <c r="J169" t="n">
         <v>105.534427</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.119453</v>
+        <v>2.061526</v>
       </c>
       <c r="F170" t="n">
-        <v>2.964649</v>
+        <v>2.880192</v>
       </c>
       <c r="G170" t="n">
-        <v>3.503181</v>
+        <v>3.412582</v>
       </c>
       <c r="H170" t="n">
-        <v>3.797896</v>
+        <v>3.691223</v>
       </c>
       <c r="I170" t="n">
-        <v>3.886264</v>
+        <v>3.729965</v>
       </c>
       <c r="J170" t="n">
         <v>5.654922</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>10.833346</v>
+        <v>10.810972</v>
       </c>
       <c r="F171" t="n">
-        <v>12.120744</v>
+        <v>12.065747</v>
       </c>
       <c r="G171" t="n">
-        <v>12.163243</v>
+        <v>12.077168</v>
       </c>
       <c r="H171" t="n">
-        <v>11.780467</v>
+        <v>11.654714</v>
       </c>
       <c r="I171" t="n">
-        <v>10.939319</v>
+        <v>10.736659</v>
       </c>
       <c r="J171" t="n">
         <v>12.3166</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>17.510662</v>
+        <v>17.755603</v>
       </c>
       <c r="F172" t="n">
-        <v>17.654981</v>
+        <v>18.05222</v>
       </c>
       <c r="G172" t="n">
-        <v>15.364808</v>
+        <v>15.816689</v>
       </c>
       <c r="H172" t="n">
-        <v>12.81451</v>
+        <v>13.320868</v>
       </c>
       <c r="I172" t="n">
-        <v>9.961395</v>
+        <v>10.627053</v>
       </c>
       <c r="J172" t="n">
         <v>0.771535</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.129994</v>
+        <v>0.122381</v>
       </c>
       <c r="F173" t="n">
-        <v>0.185147</v>
+        <v>0.172635</v>
       </c>
       <c r="G173" t="n">
-        <v>0.220923</v>
+        <v>0.205642</v>
       </c>
       <c r="H173" t="n">
-        <v>0.246856</v>
+        <v>0.227174</v>
       </c>
       <c r="I173" t="n">
-        <v>0.276687</v>
+        <v>0.247194</v>
       </c>
       <c r="J173" t="n">
         <v>0.633334</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>89.645689</v>
+        <v>90.55335599999999</v>
       </c>
       <c r="F174" t="n">
-        <v>93.66645</v>
+        <v>95.08760599999999</v>
       </c>
       <c r="G174" t="n">
-        <v>88.602242</v>
+        <v>90.24275</v>
       </c>
       <c r="H174" t="n">
-        <v>81.721169</v>
+        <v>83.64262600000001</v>
       </c>
       <c r="I174" t="n">
-        <v>70.45477099999999</v>
+        <v>73.097099</v>
       </c>
       <c r="J174" t="n">
         <v>30.425158</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.29587</v>
+        <v>0.270611</v>
       </c>
       <c r="F175" t="n">
-        <v>0.464725</v>
+        <v>0.430451</v>
       </c>
       <c r="G175" t="n">
-        <v>0.608422</v>
+        <v>0.575945</v>
       </c>
       <c r="H175" t="n">
-        <v>0.728162</v>
+        <v>0.697808</v>
       </c>
       <c r="I175" t="n">
-        <v>0.805535</v>
+        <v>0.774164</v>
       </c>
       <c r="J175" t="n">
         <v>1.049429</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.044222</v>
+        <v>0.044264</v>
       </c>
       <c r="F176" t="n">
-        <v>0.04464</v>
+        <v>0.044453</v>
       </c>
       <c r="G176" t="n">
-        <v>0.042063</v>
+        <v>0.041602</v>
       </c>
       <c r="H176" t="n">
-        <v>0.039489</v>
+        <v>0.038738</v>
       </c>
       <c r="I176" t="n">
-        <v>0.036625</v>
+        <v>0.035417</v>
       </c>
       <c r="J176" t="n">
         <v>0.047375</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>66.051537</v>
+        <v>66.05041300000001</v>
       </c>
       <c r="F177" t="n">
-        <v>92.397192</v>
+        <v>93.04733299999999</v>
       </c>
       <c r="G177" t="n">
-        <v>108.539921</v>
+        <v>110.086289</v>
       </c>
       <c r="H177" t="n">
-        <v>112.363988</v>
+        <v>114.806303</v>
       </c>
       <c r="I177" t="n">
-        <v>101.206374</v>
+        <v>104.918266</v>
       </c>
       <c r="J177" t="n">
         <v>45.966039</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.05454</v>
+        <v>0.053731</v>
       </c>
       <c r="F178" t="n">
-        <v>0.068994</v>
+        <v>0.067482</v>
       </c>
       <c r="G178" t="n">
-        <v>0.07561900000000001</v>
+        <v>0.07345599999999999</v>
       </c>
       <c r="H178" t="n">
-        <v>0.079315</v>
+        <v>0.07618800000000001</v>
       </c>
       <c r="I178" t="n">
-        <v>0.08215600000000001</v>
+        <v>0.077017</v>
       </c>
       <c r="J178" t="n">
         <v>0.146364</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.107127</v>
+        <v>0.107523</v>
       </c>
       <c r="F179" t="n">
-        <v>0.116143</v>
+        <v>0.116704</v>
       </c>
       <c r="G179" t="n">
-        <v>0.115713</v>
+        <v>0.116472</v>
       </c>
       <c r="H179" t="n">
-        <v>0.109735</v>
+        <v>0.110717</v>
       </c>
       <c r="I179" t="n">
-        <v>0.096419</v>
+        <v>0.097785</v>
       </c>
       <c r="J179" t="n">
         <v>0.066626</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4e-06</v>
+        <v>-0</v>
       </c>
       <c r="F181" t="n">
-        <v>-5e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="G181" t="n">
-        <v>-4e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>4e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="I181" t="n">
         <v>4e-06</v>
       </c>
       <c r="J181" t="n">
-        <v>-1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="K181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="L181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="O181" t="n">
         <v>4e-06</v>
-      </c>
-      <c r="L181" t="n">
-        <v>-7e-06</v>
-      </c>
-      <c r="M181" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="N181" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="O181" t="n">
-        <v>2e-06</v>
       </c>
       <c r="P181" t="n">
         <v>3e-06</v>
       </c>
       <c r="Q181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="R181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="S181" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="T181" t="n">
         <v>-6e-06</v>
       </c>
-      <c r="R181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="S181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="T181" t="n">
-        <v>-1e-06</v>
-      </c>
       <c r="U181" t="n">
-        <v>-4e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>-3e-06</v>
+        <v>-2e-06</v>
       </c>
     </row>
   </sheetData>
